--- a/Rwanda MINECOFIN-GIZ project 2026/2 Exercises/1 Introductory Exercises/Exercise 2 - SAM Analysis.xlsx
+++ b/Rwanda MINECOFIN-GIZ project 2026/2 Exercises/1 Introductory Exercises/Exercise 2 - SAM Analysis.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JTHURLOW\Dropbox (IFPRI)\Training\Bangladesh CGE Course\Exercises\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EARAGIE\IFPRI Dropbox\Emerta Aragie\Rwanda MINECOFIN-GIZ project 2026\2 Exercises\1 Introductory Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595332D7-E5C4-4750-888D-B04E5D25AD5A}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC5F4F7-016F-476F-9116-F06477657FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ex2_Question" sheetId="2" r:id="rId1"/>
-    <sheet name="Ex2_Answer" sheetId="3" r:id="rId2"/>
+    <sheet name="Ex2_Answer" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -974,14 +979,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -998,7 +1003,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1014,10 +1018,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -1025,7 +1029,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1033,23 +1036,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1062,7 +1054,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1095,9 +1087,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1135,9 +1127,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1170,26 +1162,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1222,26 +1197,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1416,19 +1374,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF7A672-2B74-4A46-B808-C8799D909395}">
   <dimension ref="A1:AB305"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:28" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -1442,7 +1400,7 @@
       <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1500,7 +1458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -1508,7 +1466,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="66"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
       <c r="I7" s="3">
@@ -1544,7 +1502,7 @@
         <v>6083.9481150695065</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
@@ -1552,7 +1510,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="67"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
       <c r="I8" s="6">
@@ -1588,7 +1546,7 @@
         <v>530.99793367786128</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1554,7 @@
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="67"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="7"/>
       <c r="I9" s="6">
@@ -1632,7 +1590,7 @@
         <v>11592.41657869403</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>3</v>
       </c>
@@ -1640,7 +1598,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="67"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="7"/>
       <c r="I10" s="6">
@@ -1676,7 +1634,7 @@
         <v>4964.714367304332</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>168</v>
       </c>
@@ -1684,7 +1642,7 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="67"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="7"/>
       <c r="I11" s="6">
@@ -1720,7 +1678,7 @@
         <v>4949.2697196303889</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -1728,7 +1686,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="67"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6">
@@ -1764,7 +1722,7 @@
         <v>2262.4772704116963</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>184</v>
       </c>
@@ -1772,7 +1730,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="67"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6">
@@ -1817,7 +1775,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -1833,7 +1791,7 @@
       <c r="E14" s="3">
         <v>218.84704685761815</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
@@ -1870,20 +1828,20 @@
       <c r="X14" s="4">
         <v>6428.5703532211328</v>
       </c>
-      <c r="Z14" s="61">
+      <c r="Z14" s="6">
         <f>X14</f>
         <v>6428.5703532211328</v>
       </c>
-      <c r="AA14" s="61">
+      <c r="AA14" s="6">
         <f>SUM(B14:H14)</f>
         <v>2860.7980276361909</v>
       </c>
-      <c r="AB14" s="61">
+      <c r="AB14" s="6">
         <f>SUM(S14:W14)</f>
         <v>3567.7723255849419</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -1899,7 +1857,7 @@
       <c r="E15" s="6">
         <v>314.27975862244585</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="6">
         <v>88.758563717962957</v>
       </c>
       <c r="G15" s="6">
@@ -1936,20 +1894,20 @@
       <c r="X15" s="7">
         <v>634.83870384962336</v>
       </c>
-      <c r="Z15" s="61">
+      <c r="Z15" s="6">
         <f t="shared" ref="Z15:Z20" si="0">X15</f>
         <v>634.83870384962336</v>
       </c>
-      <c r="AA15" s="61">
+      <c r="AA15" s="6">
         <f t="shared" ref="AA15:AA20" si="1">SUM(B15:H15)</f>
         <v>633.3102623599118</v>
       </c>
-      <c r="AB15" s="61">
+      <c r="AB15" s="6">
         <f t="shared" ref="AB15:AB20" si="2">SUM(S15:W15)</f>
         <v>1.528441489711593</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
@@ -1965,7 +1923,7 @@
       <c r="E16" s="6">
         <v>1805.2238927827259</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="6">
         <v>526.72555085137151</v>
       </c>
       <c r="G16" s="6">
@@ -2002,20 +1960,20 @@
       <c r="X16" s="7">
         <v>15149.928070463553</v>
       </c>
-      <c r="Z16" s="61">
+      <c r="Z16" s="6">
         <f t="shared" si="0"/>
         <v>15149.928070463553</v>
       </c>
-      <c r="AA16" s="61">
+      <c r="AA16" s="6">
         <f t="shared" si="1"/>
         <v>7002.1647133535807</v>
       </c>
-      <c r="AB16" s="61">
+      <c r="AB16" s="6">
         <f t="shared" si="2"/>
         <v>8147.7633571099705</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -2031,7 +1989,7 @@
       <c r="E17" s="6">
         <v>374.85065844644004</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="6">
         <v>49.087495294874827</v>
       </c>
       <c r="G17" s="6">
@@ -2068,20 +2026,20 @@
       <c r="X17" s="7">
         <v>4981.8058560754589</v>
       </c>
-      <c r="Z17" s="61">
+      <c r="Z17" s="6">
         <f t="shared" si="0"/>
         <v>4981.8058560754589</v>
       </c>
-      <c r="AA17" s="61">
+      <c r="AA17" s="6">
         <f t="shared" si="1"/>
         <v>808.57436616614427</v>
       </c>
-      <c r="AB17" s="61">
+      <c r="AB17" s="6">
         <f t="shared" si="2"/>
         <v>4173.2314899093144</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>167</v>
       </c>
@@ -2097,7 +2055,7 @@
       <c r="E18" s="6">
         <v>104.53241537752901</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="6">
         <v>76.088551577062759</v>
       </c>
       <c r="G18" s="6">
@@ -2134,20 +2092,20 @@
       <c r="X18" s="7">
         <v>5378.5714066022902</v>
       </c>
-      <c r="Z18" s="61">
+      <c r="Z18" s="6">
         <f t="shared" si="0"/>
         <v>5378.5714066022902</v>
       </c>
-      <c r="AA18" s="61">
+      <c r="AA18" s="6">
         <f t="shared" si="1"/>
         <v>4883.4956529192823</v>
       </c>
-      <c r="AB18" s="61">
+      <c r="AB18" s="6">
         <f t="shared" si="2"/>
         <v>495.07575368300843</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>9</v>
       </c>
@@ -2163,7 +2121,7 @@
       <c r="E19" s="6">
         <v>36.361870747235798</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="6">
         <v>33.664324915703766</v>
       </c>
       <c r="G19" s="6">
@@ -2200,20 +2158,20 @@
       <c r="X19" s="7">
         <v>2277.9121662753387</v>
       </c>
-      <c r="Z19" s="61">
+      <c r="Z19" s="6">
         <f t="shared" si="0"/>
         <v>2277.9121662753387</v>
       </c>
-      <c r="AA19" s="61">
+      <c r="AA19" s="6">
         <f t="shared" si="1"/>
         <v>383.45224435707019</v>
       </c>
-      <c r="AB19" s="61">
+      <c r="AB19" s="6">
         <f t="shared" si="2"/>
         <v>1894.4599219182685</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>185</v>
       </c>
@@ -2229,7 +2187,7 @@
       <c r="E20" s="9">
         <v>617.38674573713388</v>
       </c>
-      <c r="F20" s="68">
+      <c r="F20" s="9">
         <v>500.0888416258033</v>
       </c>
       <c r="G20" s="9">
@@ -2266,20 +2224,20 @@
       <c r="X20" s="10">
         <v>5779.0603770187263</v>
       </c>
-      <c r="Z20" s="61">
+      <c r="Z20" s="6">
         <f t="shared" si="0"/>
         <v>5779.0603770187263</v>
       </c>
-      <c r="AA20" s="61">
+      <c r="AA20" s="6">
         <f t="shared" si="1"/>
         <v>3195.500397984998</v>
       </c>
-      <c r="AB20" s="61">
+      <c r="AB20" s="6">
         <f t="shared" si="2"/>
         <v>2583.5599790337283</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>10</v>
       </c>
@@ -2295,7 +2253,7 @@
       <c r="E21" s="6">
         <v>1054.5939496360331</v>
       </c>
-      <c r="F21" s="67">
+      <c r="F21" s="6">
         <v>670.35889402609632</v>
       </c>
       <c r="G21" s="6">
@@ -2325,7 +2283,7 @@
         <v>6079.4216885859878</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
@@ -2341,7 +2299,7 @@
       <c r="E22" s="6">
         <v>438.63802909716787</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F22" s="6">
         <v>3004.4974976215126</v>
       </c>
       <c r="G22" s="6">
@@ -2371,7 +2329,7 @@
         <v>10181.806872848019</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>188</v>
       </c>
@@ -2379,7 +2337,7 @@
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
-      <c r="F23" s="69"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="12"/>
@@ -2413,7 +2371,7 @@
         <v>10189.884565311602</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -2421,7 +2379,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="66"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="3"/>
@@ -2457,7 +2415,7 @@
         <v>8616.6805824517432</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -2465,7 +2423,7 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="68"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="10"/>
       <c r="I25" s="9"/>
@@ -2501,7 +2459,7 @@
         <v>5775.3997392920746</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -2517,7 +2475,7 @@
       <c r="E26" s="6">
         <v>0</v>
       </c>
-      <c r="F26" s="67">
+      <c r="F26" s="6">
         <v>0</v>
       </c>
       <c r="G26" s="6">
@@ -2571,7 +2529,7 @@
         <v>1634.0800405341656</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>15</v>
       </c>
@@ -2579,7 +2537,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="67"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
       <c r="I27" s="6"/>
@@ -2611,7 +2569,7 @@
         <v>5218.0019059164133</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>16</v>
       </c>
@@ -2619,7 +2577,7 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="67"/>
+      <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
       <c r="I28" s="6">
@@ -2667,7 +2625,7 @@
         <v>3992.5392070432972</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>17</v>
       </c>
@@ -2683,7 +2641,7 @@
       <c r="E29" s="12">
         <v>4964.7143673043302</v>
       </c>
-      <c r="F29" s="69">
+      <c r="F29" s="12">
         <v>4949.269719630388</v>
       </c>
       <c r="G29" s="12">
@@ -2739,42 +2697,42 @@
       </c>
       <c r="X29" s="17"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A30" s="63"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="R30" s="64"/>
-      <c r="S30" s="64"/>
-      <c r="T30" s="64"/>
-      <c r="U30" s="64"/>
-    </row>
-    <row r="31" spans="1:28" ht="18" x14ac:dyDescent="0.35">
-      <c r="A31" s="40" t="s">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A30" s="58"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="59"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="59"/>
+      <c r="T30" s="59"/>
+      <c r="U30" s="59"/>
+    </row>
+    <row r="31" spans="1:28" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" s="24" t="s">
         <v>39</v>
       </c>
       <c r="Q33" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -2785,16 +2743,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="90" t="s">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B35" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="91"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="92"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="79"/>
       <c r="Q35" t="s">
         <v>1</v>
       </c>
@@ -2802,7 +2760,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>0</v>
       </c>
@@ -2834,7 +2792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
         <v>5</v>
       </c>
@@ -2853,7 +2811,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="21" t="s">
         <v>6</v>
       </c>
@@ -2872,7 +2830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>7</v>
       </c>
@@ -2891,7 +2849,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
         <v>8</v>
       </c>
@@ -2910,7 +2868,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>167</v>
       </c>
@@ -2929,7 +2887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>9</v>
       </c>
@@ -2948,7 +2906,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>185</v>
       </c>
@@ -2967,7 +2925,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
         <v>10</v>
       </c>
@@ -2986,7 +2944,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
         <v>11</v>
       </c>
@@ -3005,7 +2963,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
         <v>17</v>
       </c>
@@ -3017,7 +2975,7 @@
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
       <c r="I46" s="17"/>
-      <c r="J46" s="51">
+      <c r="J46" s="49">
         <v>36021.141652683138</v>
       </c>
       <c r="Q46" t="s">
@@ -3027,7 +2985,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q47" t="s">
         <v>185</v>
       </c>
@@ -3035,7 +2993,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q48" t="s">
         <v>10</v>
       </c>
@@ -3043,8 +3001,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" s="25" t="s">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A49" s="24" t="s">
         <v>41</v>
       </c>
       <c r="Q49" t="s">
@@ -3054,7 +3012,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -3065,7 +3023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B51" s="2" t="s">
         <v>0</v>
       </c>
@@ -3097,43 +3055,19 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A52" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="12">
-        <f>SUM(B44:B45)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="12">
-        <f t="shared" ref="C52:I52" si="3">SUM(C44:C45)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E52" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F52" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G52" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="12">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="51">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="49">
         <v>16253.845987905948</v>
       </c>
       <c r="Q52" t="s">
@@ -3143,7 +3077,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q53" t="s">
         <v>15</v>
       </c>
@@ -3151,7 +3085,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q54" t="s">
         <v>16</v>
       </c>
@@ -3159,18 +3093,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A55" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
       <c r="Q55" t="s">
         <v>17</v>
       </c>
@@ -3178,12 +3112,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B57" s="2" t="s">
         <v>0</v>
       </c>
@@ -3209,52 +3143,49 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A58" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="28"/>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="H59" s="52">
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="27"/>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="H59" s="50">
         <v>23.930265532624151</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="30" t="s">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A61" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" s="30" t="s">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A62" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B62" s="62">
-        <f>C58/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="25" t="s">
+      <c r="B62" s="57"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B67" s="2" t="s">
         <v>0</v>
       </c>
@@ -3280,134 +3211,134 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="52">
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="50">
         <v>37.4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="36"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B69" s="33"/>
+      <c r="C69" s="33"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
+      <c r="G69" s="33"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="35"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="34"/>
-      <c r="I70" s="36"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="30" t="s">
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="35"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="30" t="s">
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="30"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="30" t="s">
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="29"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="30" t="s">
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="28"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="25" t="s">
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B82" s="2" t="s">
         <v>0</v>
       </c>
@@ -3433,204 +3364,204 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="54"/>
-      <c r="C83" s="31"/>
-      <c r="D83" s="31"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="33"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B83" s="52"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="32"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="55"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="39"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B84" s="53"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="38"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="55"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="39"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B85" s="53"/>
+      <c r="C85" s="36"/>
+      <c r="D85" s="36"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="36"/>
+      <c r="G85" s="36"/>
+      <c r="H85" s="36"/>
+      <c r="I85" s="38"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B86" s="55"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="39"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B86" s="53"/>
+      <c r="C86" s="36"/>
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="36"/>
+      <c r="G86" s="36"/>
+      <c r="H86" s="36"/>
+      <c r="I86" s="38"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="55"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="39"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B87" s="53"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="38"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="55"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="39"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B88" s="53"/>
+      <c r="C88" s="36"/>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="36"/>
+      <c r="I88" s="38"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B89" s="73"/>
-      <c r="C89" s="34"/>
-      <c r="D89" s="34"/>
-      <c r="E89" s="34"/>
-      <c r="F89" s="34"/>
-      <c r="G89" s="34"/>
-      <c r="H89" s="34"/>
-      <c r="I89" s="36"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B89" s="60"/>
+      <c r="C89" s="33"/>
+      <c r="D89" s="33"/>
+      <c r="E89" s="33"/>
+      <c r="F89" s="33"/>
+      <c r="G89" s="33"/>
+      <c r="H89" s="33"/>
+      <c r="I89" s="35"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B90" s="54"/>
-      <c r="C90" s="31"/>
-      <c r="D90" s="31"/>
-      <c r="E90" s="31"/>
-      <c r="F90" s="31"/>
-      <c r="G90" s="31"/>
-      <c r="H90" s="31"/>
-      <c r="I90" s="33"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B90" s="52"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="32"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="34"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="34"/>
-      <c r="H91" s="34"/>
-      <c r="I91" s="36"/>
-      <c r="J91" s="52">
+      <c r="B91" s="60"/>
+      <c r="C91" s="33"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="33"/>
+      <c r="F91" s="33"/>
+      <c r="G91" s="33"/>
+      <c r="H91" s="33"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="50">
         <v>28.251211450621334</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="73"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="26"/>
-      <c r="I92" s="28"/>
-      <c r="J92" s="52">
+      <c r="B92" s="60"/>
+      <c r="C92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
+      <c r="H92" s="25"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="30" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="28" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="30" t="s">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="B96" s="62">
+      <c r="B96" s="57">
         <f>B85/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="30"/>
-      <c r="B97" s="29"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="30" t="s">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="29"/>
+      <c r="B97" s="28"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B98" s="29" t="s">
+      <c r="B98" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="30" t="s">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B99" s="62">
+      <c r="B99" s="57">
         <f>F87/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A102" s="40" t="s">
+    <row r="102" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A102" s="39" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="25" t="s">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A104" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
-      <c r="I104" s="25"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B106" s="2" t="s">
         <v>5</v>
       </c>
@@ -3656,7 +3587,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="20" t="s">
         <v>62</v>
       </c>
@@ -3668,9 +3599,9 @@
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
       <c r="I107" s="14"/>
-      <c r="J107" s="51"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J107" s="49"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="22" t="s">
         <v>63</v>
       </c>
@@ -3682,29 +3613,29 @@
       <c r="G108" s="9"/>
       <c r="H108" s="10"/>
       <c r="I108" s="16"/>
-      <c r="J108" s="51">
+      <c r="J108" s="49">
         <v>3263.3659055205276</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="25" t="s">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A111" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
-      <c r="I111" s="25"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B113" s="2" t="s">
         <v>5</v>
       </c>
@@ -3730,115 +3661,115 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B114" s="54"/>
-      <c r="C114" s="31"/>
-      <c r="D114" s="31"/>
-      <c r="E114" s="31"/>
-      <c r="F114" s="31"/>
-      <c r="G114" s="31"/>
-      <c r="H114" s="32"/>
-      <c r="I114" s="33"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B114" s="52"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
+      <c r="G114" s="30"/>
+      <c r="H114" s="31"/>
+      <c r="I114" s="32"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B115" s="73"/>
-      <c r="C115" s="34"/>
-      <c r="D115" s="34"/>
-      <c r="E115" s="34"/>
-      <c r="F115" s="34"/>
-      <c r="G115" s="34"/>
-      <c r="H115" s="35"/>
-      <c r="I115" s="36"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H116" s="52">
+      <c r="B115" s="60"/>
+      <c r="C115" s="33"/>
+      <c r="D115" s="33"/>
+      <c r="E115" s="33"/>
+      <c r="F115" s="33"/>
+      <c r="G115" s="33"/>
+      <c r="H115" s="34"/>
+      <c r="I115" s="35"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H116" s="50">
         <v>3.2337949558400831</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="30" t="s">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A118" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B118" s="29" t="s">
+      <c r="B118" s="28" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="30" t="s">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A119" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B119" s="29"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="30"/>
-      <c r="B120" s="29"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="30" t="s">
+      <c r="B119" s="28"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A120" s="29"/>
+      <c r="B120" s="28"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A121" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="28" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="30" t="s">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A122" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="B122" s="29"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A125" s="25" t="s">
+      <c r="B122" s="28"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A125" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
-      <c r="D125" s="25"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25"/>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B125" s="24"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B127" s="41" t="s">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B127" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="42" t="s">
+      <c r="C127" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D127" s="42" t="s">
+      <c r="D127" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="42" t="s">
+      <c r="E127" s="41" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G127" s="42" t="s">
+      <c r="G127" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H127" s="43" t="s">
+      <c r="H127" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="I127" s="43" t="s">
+      <c r="I127" s="42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A128" s="44" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A128" s="43" t="s">
         <v>78</v>
       </c>
       <c r="B128" s="2"/>
@@ -3849,15 +3780,15 @@
       <c r="G128" s="3"/>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
-      <c r="J128" s="51">
+      <c r="J128" s="49">
         <v>40630.68693350612</v>
       </c>
-      <c r="K128" s="53" t="s">
+      <c r="K128" s="51" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A129" s="47" t="s">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A129" s="46" t="s">
         <v>79</v>
       </c>
       <c r="B129" s="5"/>
@@ -3868,15 +3799,15 @@
       <c r="G129" s="6"/>
       <c r="H129" s="7"/>
       <c r="I129" s="7"/>
-      <c r="J129" s="51">
+      <c r="J129" s="49">
         <v>19767.295664777179</v>
       </c>
-      <c r="K129" s="53" t="s">
+      <c r="K129" s="51" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A130" s="50" t="s">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A130" s="48" t="s">
         <v>80</v>
       </c>
       <c r="B130" s="8"/>
@@ -3887,32 +3818,32 @@
       <c r="G130" s="9"/>
       <c r="H130" s="10"/>
       <c r="I130" s="10"/>
-      <c r="K130" s="53" t="s">
+      <c r="K130" s="51" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H131" s="51">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H131" s="49">
         <v>2583.5599790337283</v>
       </c>
-      <c r="K131" s="53"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K132" s="53"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A133" s="25" t="s">
+      <c r="K131" s="51"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K132" s="51"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A133" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="K133" s="53"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K133" s="51"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>82</v>
       </c>
-      <c r="K134" s="53"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K134" s="51"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B135" s="2" t="s">
         <v>5</v>
       </c>
@@ -3937,136 +3868,136 @@
       <c r="I135" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K135" s="53"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K135" s="51"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B136" s="31"/>
-      <c r="C136" s="31"/>
-      <c r="D136" s="31"/>
-      <c r="E136" s="31"/>
-      <c r="F136" s="31"/>
-      <c r="G136" s="31"/>
-      <c r="H136" s="31"/>
-      <c r="I136" s="33"/>
-      <c r="J136" s="52">
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="30"/>
+      <c r="G136" s="30"/>
+      <c r="H136" s="30"/>
+      <c r="I136" s="32"/>
+      <c r="J136" s="50">
         <v>9.2270609851760241</v>
       </c>
-      <c r="K136" s="53" t="s">
+      <c r="K136" s="51" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B137" s="34"/>
-      <c r="C137" s="34"/>
-      <c r="D137" s="34"/>
-      <c r="E137" s="34"/>
-      <c r="F137" s="34"/>
-      <c r="G137" s="34"/>
-      <c r="H137" s="34"/>
-      <c r="I137" s="36"/>
-      <c r="J137" s="52">
+      <c r="B137" s="33"/>
+      <c r="C137" s="33"/>
+      <c r="D137" s="33"/>
+      <c r="E137" s="33"/>
+      <c r="F137" s="33"/>
+      <c r="G137" s="33"/>
+      <c r="H137" s="33"/>
+      <c r="I137" s="35"/>
+      <c r="J137" s="50">
         <v>9.0595848876362499</v>
       </c>
-      <c r="K137" s="53" t="s">
+      <c r="K137" s="51" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H138" s="52">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H138" s="50">
         <v>1.8719995618541665</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A140" s="30" t="s">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A140" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="28" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A141" s="30" t="s">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A141" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B141" s="29"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A142" s="30"/>
-      <c r="B142" s="29"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A143" s="30" t="s">
+      <c r="B141" s="28"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A142" s="29"/>
+      <c r="B142" s="28"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A143" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="28" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A144" s="30" t="s">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A144" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B144" s="29"/>
-    </row>
-    <row r="147" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A147" s="40" t="s">
+      <c r="B144" s="28"/>
+    </row>
+    <row r="147" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A147" s="39" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="25" t="s">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" s="24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B151" s="44" t="s">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B151" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C151" s="45" t="s">
+      <c r="C151" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D151" s="45" t="s">
+      <c r="D151" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E151" s="45" t="s">
+      <c r="E151" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F151" s="46" t="s">
+      <c r="F151" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G151" s="46" t="s">
+      <c r="G151" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B152" s="47" t="s">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B152" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C152" s="48" t="s">
+      <c r="C152" t="s">
         <v>101</v>
       </c>
-      <c r="D152" s="48" t="s">
+      <c r="D152" t="s">
         <v>101</v>
       </c>
-      <c r="E152" s="48" t="s">
+      <c r="E152" t="s">
         <v>103</v>
       </c>
-      <c r="F152" s="49"/>
-      <c r="G152" s="49"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="44" t="s">
+      <c r="F152" s="47"/>
+      <c r="G152" s="47"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B153" s="2"/>
@@ -4076,8 +4007,8 @@
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="47" t="s">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B154" s="5"/>
@@ -4087,8 +4018,8 @@
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="47" t="s">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A155" s="46" t="s">
         <v>7</v>
       </c>
       <c r="B155" s="5"/>
@@ -4098,8 +4029,8 @@
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="47" t="s">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A156" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B156" s="5"/>
@@ -4109,8 +4040,8 @@
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="47" t="s">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="46" t="s">
         <v>167</v>
       </c>
       <c r="B157" s="5"/>
@@ -4120,8 +4051,8 @@
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="47" t="s">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158" s="46" t="s">
         <v>9</v>
       </c>
       <c r="B158" s="5"/>
@@ -4131,8 +4062,8 @@
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="47" t="s">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B159" s="5"/>
@@ -4142,8 +4073,8 @@
       <c r="F159" s="10"/>
       <c r="G159" s="7"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="41" t="s">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B160" s="11"/>
@@ -4152,744 +4083,744 @@
       <c r="E160" s="12"/>
       <c r="F160" s="13"/>
       <c r="G160" s="13"/>
-      <c r="H160" s="57">
+      <c r="H160" s="49">
         <v>40630.68693350612</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="25" t="s">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="24" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B165" s="44" t="s">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B165" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C165" s="45" t="s">
+      <c r="C165" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D165" s="45" t="s">
+      <c r="D165" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E165" s="45" t="s">
+      <c r="E165" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F165" s="46" t="s">
+      <c r="F165" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G165" s="46" t="s">
+      <c r="G165" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B166" s="47" t="s">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B166" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C166" s="48" t="s">
+      <c r="C166" t="s">
         <v>101</v>
       </c>
-      <c r="D166" s="48" t="s">
+      <c r="D166" t="s">
         <v>101</v>
       </c>
-      <c r="E166" s="48" t="s">
+      <c r="E166" t="s">
         <v>103</v>
       </c>
-      <c r="F166" s="49"/>
-      <c r="G166" s="49"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="44" t="s">
+      <c r="F166" s="47"/>
+      <c r="G166" s="47"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B167" s="54"/>
-      <c r="C167" s="31"/>
-      <c r="D167" s="31"/>
-      <c r="E167" s="31"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="47" t="s">
+      <c r="B167" s="52"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="30"/>
+      <c r="E167" s="30"/>
+      <c r="F167" s="31"/>
+      <c r="G167" s="31"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A168" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B168" s="55"/>
-      <c r="C168" s="37"/>
-      <c r="D168" s="37"/>
-      <c r="E168" s="37"/>
-      <c r="F168" s="38"/>
-      <c r="G168" s="38"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="47" t="s">
+      <c r="B168" s="53"/>
+      <c r="C168" s="36"/>
+      <c r="D168" s="36"/>
+      <c r="E168" s="36"/>
+      <c r="F168" s="37"/>
+      <c r="G168" s="37"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B169" s="55"/>
-      <c r="C169" s="37"/>
-      <c r="D169" s="37"/>
-      <c r="E169" s="37"/>
-      <c r="F169" s="38"/>
-      <c r="G169" s="38"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="47" t="s">
+      <c r="B169" s="53"/>
+      <c r="C169" s="36"/>
+      <c r="D169" s="36"/>
+      <c r="E169" s="36"/>
+      <c r="F169" s="37"/>
+      <c r="G169" s="37"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B170" s="55"/>
-      <c r="C170" s="37"/>
-      <c r="D170" s="37"/>
-      <c r="E170" s="37"/>
-      <c r="F170" s="38"/>
-      <c r="G170" s="38"/>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="47" t="s">
+      <c r="B170" s="53"/>
+      <c r="C170" s="36"/>
+      <c r="D170" s="36"/>
+      <c r="E170" s="36"/>
+      <c r="F170" s="37"/>
+      <c r="G170" s="37"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B171" s="55"/>
-      <c r="C171" s="37"/>
-      <c r="D171" s="37"/>
-      <c r="E171" s="37"/>
-      <c r="F171" s="38"/>
-      <c r="G171" s="38"/>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="47" t="s">
+      <c r="B171" s="53"/>
+      <c r="C171" s="36"/>
+      <c r="D171" s="36"/>
+      <c r="E171" s="36"/>
+      <c r="F171" s="37"/>
+      <c r="G171" s="37"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B172" s="55"/>
-      <c r="C172" s="37"/>
-      <c r="D172" s="37"/>
-      <c r="E172" s="37"/>
-      <c r="F172" s="38"/>
-      <c r="G172" s="38"/>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="47" t="s">
+      <c r="B172" s="53"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="37"/>
+      <c r="G172" s="37"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B173" s="55"/>
-      <c r="C173" s="37"/>
-      <c r="D173" s="37"/>
-      <c r="E173" s="37"/>
-      <c r="F173" s="38"/>
-      <c r="G173" s="38"/>
-      <c r="H173" s="56">
+      <c r="B173" s="53"/>
+      <c r="C173" s="36"/>
+      <c r="D173" s="36"/>
+      <c r="E173" s="36"/>
+      <c r="F173" s="37"/>
+      <c r="G173" s="37"/>
+      <c r="H173" s="50">
         <v>14.223388313558196</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="41" t="s">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A174" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B174" s="58"/>
-      <c r="C174" s="26"/>
-      <c r="D174" s="26"/>
-      <c r="E174" s="26"/>
-      <c r="F174" s="27"/>
-      <c r="G174" s="27"/>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F175" s="56">
+      <c r="B174" s="54"/>
+      <c r="C174" s="25"/>
+      <c r="D174" s="25"/>
+      <c r="E174" s="25"/>
+      <c r="F174" s="26"/>
+      <c r="G174" s="26"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F175" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="30" t="s">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A177" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="B177" s="29" t="s">
+      <c r="B177" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="30" t="s">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B178" s="29"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="30"/>
-      <c r="B179" s="29"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="30" t="s">
+      <c r="B178" s="28"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A179" s="29"/>
+      <c r="B179" s="28"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A180" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="B180" s="29" t="s">
+      <c r="B180" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="30" t="s">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A181" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B181" s="29"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="25" t="s">
+      <c r="B181" s="28"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A184" s="24" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="46"/>
-      <c r="B186" s="44" t="s">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A186" s="45"/>
+      <c r="B186" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C186" s="45" t="s">
+      <c r="C186" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D186" s="45" t="s">
+      <c r="D186" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E186" s="45" t="s">
+      <c r="E186" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F186" s="46" t="s">
+      <c r="F186" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G186" s="46" t="s">
+      <c r="G186" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="60"/>
-      <c r="B187" s="47" t="s">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A187" s="56"/>
+      <c r="B187" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C187" s="48" t="s">
+      <c r="C187" t="s">
         <v>101</v>
       </c>
-      <c r="D187" s="48" t="s">
+      <c r="D187" t="s">
         <v>101</v>
       </c>
-      <c r="E187" s="48" t="s">
+      <c r="E187" t="s">
         <v>103</v>
       </c>
-      <c r="F187" s="49"/>
-      <c r="G187" s="49"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="44" t="s">
+      <c r="F187" s="47"/>
+      <c r="G187" s="47"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A188" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B188" s="81"/>
-      <c r="C188" s="82"/>
-      <c r="D188" s="82"/>
-      <c r="E188" s="82"/>
-      <c r="F188" s="83"/>
+      <c r="B188" s="68"/>
+      <c r="C188" s="69"/>
+      <c r="D188" s="69"/>
+      <c r="E188" s="69"/>
+      <c r="F188" s="70"/>
       <c r="G188" s="4"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="47" t="s">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A189" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B189" s="84"/>
-      <c r="C189" s="85"/>
-      <c r="D189" s="85"/>
-      <c r="E189" s="85"/>
-      <c r="F189" s="86"/>
+      <c r="B189" s="71"/>
+      <c r="C189" s="72"/>
+      <c r="D189" s="72"/>
+      <c r="E189" s="72"/>
+      <c r="F189" s="73"/>
       <c r="G189" s="7"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="47" t="s">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A190" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B190" s="84"/>
-      <c r="C190" s="85"/>
-      <c r="D190" s="85"/>
-      <c r="E190" s="85"/>
-      <c r="F190" s="86"/>
+      <c r="B190" s="71"/>
+      <c r="C190" s="72"/>
+      <c r="D190" s="72"/>
+      <c r="E190" s="72"/>
+      <c r="F190" s="73"/>
       <c r="G190" s="7"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="47" t="s">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A191" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B191" s="84"/>
-      <c r="C191" s="85"/>
-      <c r="D191" s="85"/>
-      <c r="E191" s="85"/>
-      <c r="F191" s="86"/>
+      <c r="B191" s="71"/>
+      <c r="C191" s="72"/>
+      <c r="D191" s="72"/>
+      <c r="E191" s="72"/>
+      <c r="F191" s="73"/>
       <c r="G191" s="7"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="47" t="s">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A192" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B192" s="84"/>
-      <c r="C192" s="85"/>
-      <c r="D192" s="85"/>
-      <c r="E192" s="85"/>
-      <c r="F192" s="86"/>
+      <c r="B192" s="71"/>
+      <c r="C192" s="72"/>
+      <c r="D192" s="72"/>
+      <c r="E192" s="72"/>
+      <c r="F192" s="73"/>
       <c r="G192" s="7"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="47" t="s">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A193" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B193" s="84"/>
-      <c r="C193" s="85"/>
-      <c r="D193" s="85"/>
-      <c r="E193" s="85"/>
-      <c r="F193" s="86"/>
+      <c r="B193" s="71"/>
+      <c r="C193" s="72"/>
+      <c r="D193" s="72"/>
+      <c r="E193" s="72"/>
+      <c r="F193" s="73"/>
       <c r="G193" s="7"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="47" t="s">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A194" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B194" s="84"/>
-      <c r="C194" s="85"/>
-      <c r="D194" s="85"/>
-      <c r="E194" s="85"/>
-      <c r="F194" s="86"/>
+      <c r="B194" s="71"/>
+      <c r="C194" s="72"/>
+      <c r="D194" s="72"/>
+      <c r="E194" s="72"/>
+      <c r="F194" s="73"/>
       <c r="G194" s="7"/>
-      <c r="H194" s="56">
+      <c r="H194" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="41" t="s">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A195" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B195" s="87"/>
-      <c r="C195" s="88"/>
-      <c r="D195" s="88"/>
-      <c r="E195" s="88"/>
-      <c r="F195" s="89"/>
-      <c r="G195" s="27"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F196" s="56">
+      <c r="B195" s="74"/>
+      <c r="C195" s="75"/>
+      <c r="D195" s="75"/>
+      <c r="E195" s="75"/>
+      <c r="F195" s="76"/>
+      <c r="G195" s="26"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F196" s="50">
         <v>8.0317763538213551</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A198" s="40" t="s">
+    <row r="198" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A198" s="39" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" s="25" t="s">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A200" s="24" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B202" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C202" s="46" t="s">
+      <c r="C202" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D202" s="46" t="s">
+      <c r="D202" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="44" t="s">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A203" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
-      <c r="E203" s="53" t="s">
+      <c r="E203" s="51" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" s="47" t="s">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A204" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B204" s="5"/>
       <c r="C204" s="7"/>
       <c r="D204" s="7"/>
-      <c r="E204" s="53" t="s">
+      <c r="E204" s="51" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" s="47" t="s">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A205" s="46" t="s">
         <v>7</v>
       </c>
       <c r="B205" s="5"/>
       <c r="C205" s="7"/>
       <c r="D205" s="7"/>
-      <c r="E205" s="53" t="s">
+      <c r="E205" s="51" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" s="47" t="s">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A206" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B206" s="5"/>
       <c r="C206" s="7"/>
       <c r="D206" s="7"/>
-      <c r="E206" s="53" t="s">
+      <c r="E206" s="51" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" s="47" t="s">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A207" s="46" t="s">
         <v>167</v>
       </c>
       <c r="B207" s="5"/>
       <c r="C207" s="7"/>
       <c r="D207" s="7"/>
-      <c r="E207" s="53" t="s">
+      <c r="E207" s="51" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" s="47" t="s">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A208" s="46" t="s">
         <v>9</v>
       </c>
       <c r="B208" s="5"/>
       <c r="C208" s="7"/>
       <c r="D208" s="7"/>
-      <c r="E208" s="53" t="s">
+      <c r="E208" s="51" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="47" t="s">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B209" s="5"/>
       <c r="C209" s="7"/>
       <c r="D209" s="7"/>
-      <c r="E209" s="53" t="s">
+      <c r="E209" s="51" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="47" t="s">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210" s="46" t="s">
         <v>14</v>
       </c>
       <c r="B210" s="5"/>
       <c r="C210" s="7"/>
       <c r="D210" s="7"/>
-      <c r="E210" s="53" t="s">
+      <c r="E210" s="51" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A211" s="47" t="s">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" s="46" t="s">
         <v>15</v>
       </c>
       <c r="B211" s="8"/>
       <c r="C211" s="10"/>
       <c r="D211" s="7"/>
-      <c r="E211" s="53" t="s">
+      <c r="E211" s="51" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" s="41" t="s">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B212" s="11"/>
       <c r="C212" s="13"/>
       <c r="D212" s="13"/>
-      <c r="E212" s="53" t="s">
+      <c r="E212" s="51" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C213" s="51">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C213" s="49">
         <v>5774.3743051158172</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" s="30" t="s">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="B215" s="29" t="s">
+      <c r="B215" s="28" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="30" t="s">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="B216" s="29"/>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="30"/>
-      <c r="B217" s="29"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="30" t="s">
+      <c r="B216" s="28"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" s="29"/>
+      <c r="B217" s="28"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="B218" s="29" t="s">
+      <c r="B218" s="28" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="30" t="s">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="B219" s="29"/>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="30"/>
-      <c r="B220" s="29"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="30" t="s">
+      <c r="B219" s="28"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" s="29"/>
+      <c r="B220" s="28"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="B221" s="29" t="s">
+      <c r="B221" s="28" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" s="30" t="s">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B222" s="29"/>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" s="30"/>
-      <c r="B223" s="29"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" s="30" t="s">
+      <c r="B222" s="28"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" s="29"/>
+      <c r="B223" s="28"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B224" s="29" t="s">
+      <c r="B224" s="28" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="30" t="s">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B225" s="29"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B226" s="29"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B227" s="29"/>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="25" t="s">
+      <c r="B225" s="28"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B226" s="28"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B227" s="28"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B230" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C230" s="46" t="s">
+      <c r="C230" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="46" t="s">
+      <c r="D230" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="44" t="s">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A231" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B231" s="54"/>
-      <c r="C231" s="32"/>
-      <c r="D231" s="32"/>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="47" t="s">
+      <c r="B231" s="52"/>
+      <c r="C231" s="31"/>
+      <c r="D231" s="31"/>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B232" s="55"/>
-      <c r="C232" s="38"/>
-      <c r="D232" s="38"/>
-    </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="47" t="s">
+      <c r="B232" s="53"/>
+      <c r="C232" s="37"/>
+      <c r="D232" s="37"/>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B233" s="55"/>
-      <c r="C233" s="38"/>
-      <c r="D233" s="38"/>
-    </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A234" s="47" t="s">
+      <c r="B233" s="53"/>
+      <c r="C233" s="37"/>
+      <c r="D233" s="37"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A234" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B234" s="55"/>
-      <c r="C234" s="38"/>
-      <c r="D234" s="38"/>
-    </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A235" s="47" t="s">
+      <c r="B234" s="53"/>
+      <c r="C234" s="37"/>
+      <c r="D234" s="37"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A235" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B235" s="55"/>
-      <c r="C235" s="38"/>
-      <c r="D235" s="38"/>
-    </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A236" s="47" t="s">
+      <c r="B235" s="53"/>
+      <c r="C235" s="37"/>
+      <c r="D235" s="37"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B236" s="55"/>
-      <c r="C236" s="38"/>
-      <c r="D236" s="38"/>
-    </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A237" s="47" t="s">
+      <c r="B236" s="53"/>
+      <c r="C236" s="37"/>
+      <c r="D236" s="37"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B237" s="55"/>
-      <c r="C237" s="38"/>
-      <c r="D237" s="38"/>
-    </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A238" s="47" t="s">
+      <c r="B237" s="53"/>
+      <c r="C237" s="37"/>
+      <c r="D237" s="37"/>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B238" s="55"/>
-      <c r="C238" s="38"/>
-      <c r="D238" s="38"/>
-    </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A239" s="47" t="s">
+      <c r="B238" s="53"/>
+      <c r="C238" s="37"/>
+      <c r="D238" s="37"/>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B239" s="55"/>
-      <c r="C239" s="38"/>
-      <c r="D239" s="38"/>
-      <c r="E239" s="52">
+      <c r="B239" s="53"/>
+      <c r="C239" s="37"/>
+      <c r="D239" s="37"/>
+      <c r="E239" s="50">
         <v>20.04390727542393</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A240" s="41" t="s">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B240" s="58"/>
-      <c r="C240" s="27"/>
-      <c r="D240" s="27"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B241" s="29"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B242" s="29"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="30" t="s">
+      <c r="B240" s="54"/>
+      <c r="C240" s="26"/>
+      <c r="D240" s="26"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B241" s="28"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B242" s="28"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B243" s="29" t="s">
+      <c r="B243" s="28" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="30" t="s">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="B244" s="62">
+      <c r="B244" s="57">
         <f>C238/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="30"/>
-      <c r="B245" s="29"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="30" t="s">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="29"/>
+      <c r="B245" s="28"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B246" s="29" t="s">
+      <c r="B246" s="28" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="30" t="s">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B247" s="62">
+      <c r="B247" s="57">
         <f>B237/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="30"/>
-      <c r="B248" s="29"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="30" t="s">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="29"/>
+      <c r="B248" s="28"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="B249" s="29" t="s">
+      <c r="B249" s="28" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="30" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B250" s="62">
+      <c r="B250" s="57">
         <f>B239/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="25" t="s">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="24" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B255" s="41" t="s">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B255" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C255" s="42" t="s">
+      <c r="C255" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D255" s="42" t="s">
+      <c r="D255" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="42" t="s">
+      <c r="E255" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F255" s="43" t="s">
+      <c r="F255" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="G255" s="43" t="s">
+      <c r="G255" s="42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="44" t="s">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B256" s="2"/>
@@ -4899,8 +4830,8 @@
       <c r="F256" s="4"/>
       <c r="G256" s="4"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="47" t="s">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A257" s="46" t="s">
         <v>13</v>
       </c>
       <c r="B257" s="8"/>
@@ -4910,8 +4841,8 @@
       <c r="F257" s="10"/>
       <c r="G257" s="7"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="41" t="s">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A258" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B258" s="11"/>
@@ -4920,301 +4851,286 @@
       <c r="E258" s="12"/>
       <c r="F258" s="13"/>
       <c r="G258" s="13"/>
-      <c r="H258" s="51">
+      <c r="H258" s="49">
         <v>14392.080321743819</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="25" t="s">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A261" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B263" s="41" t="s">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B263" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C263" s="42" t="s">
+      <c r="C263" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D263" s="42" t="s">
+      <c r="D263" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="E263" s="42" t="s">
+      <c r="E263" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F263" s="42" t="s">
+      <c r="F263" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G263" s="24" t="s">
+      <c r="G263" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="44" t="s">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A264" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B264" s="54"/>
-      <c r="C264" s="65"/>
-      <c r="D264" s="65"/>
-      <c r="E264" s="65"/>
-      <c r="F264" s="65"/>
-      <c r="G264" s="33"/>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="47" t="s">
+      <c r="B264" s="52"/>
+      <c r="C264" s="30"/>
+      <c r="D264" s="30"/>
+      <c r="E264" s="30"/>
+      <c r="F264" s="30"/>
+      <c r="G264" s="32"/>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A265" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B265" s="55"/>
-      <c r="C265" s="37"/>
-      <c r="D265" s="37"/>
-      <c r="E265" s="37"/>
-      <c r="F265" s="37"/>
-      <c r="G265" s="39"/>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="41" t="s">
+      <c r="B265" s="53"/>
+      <c r="C265" s="36"/>
+      <c r="D265" s="36"/>
+      <c r="E265" s="36"/>
+      <c r="F265" s="36"/>
+      <c r="G265" s="38"/>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A266" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B266" s="58"/>
-      <c r="C266" s="26"/>
-      <c r="D266" s="26"/>
-      <c r="E266" s="26"/>
-      <c r="F266" s="26"/>
-      <c r="G266" s="28"/>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F267" s="52">
+      <c r="B266" s="54"/>
+      <c r="C266" s="25"/>
+      <c r="D266" s="25"/>
+      <c r="E266" s="25"/>
+      <c r="F266" s="25"/>
+      <c r="G266" s="27"/>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F267" s="50">
         <v>5.1397642141104685</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="30" t="s">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A269" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="B269" s="29" t="s">
+      <c r="B269" s="28" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="30" t="s">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A270" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B270" s="29"/>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A271" s="30"/>
-      <c r="B271" s="29"/>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A272" s="30" t="s">
+      <c r="B270" s="28"/>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A271" s="29"/>
+      <c r="B271" s="28"/>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A272" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="B272" s="29" t="s">
+      <c r="B272" s="28" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A273" s="30" t="s">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A273" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="B273" s="29"/>
-    </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A274" s="30"/>
-      <c r="B274" s="29"/>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A275" s="30" t="s">
+      <c r="B273" s="28"/>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A274" s="29"/>
+      <c r="B274" s="28"/>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A275" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B275" s="29" t="s">
+      <c r="B275" s="28" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A276" s="30" t="s">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A276" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="B276" s="29"/>
-    </row>
-    <row r="279" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A279" s="40" t="s">
+      <c r="B276" s="28"/>
+    </row>
+    <row r="279" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A279" s="39" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A280" s="72"/>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A281" s="25" t="s">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A281" s="24" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A283" s="44" t="s">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A283" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="B283" s="45"/>
-      <c r="C283" s="46"/>
+      <c r="B283" s="44"/>
+      <c r="C283" s="45"/>
       <c r="D283" s="14"/>
-      <c r="L283" s="61"/>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A284" s="47" t="s">
+      <c r="L283" s="6"/>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A284" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="B284" s="48"/>
-      <c r="C284" s="49"/>
+      <c r="C284" s="47"/>
       <c r="D284" s="15"/>
-      <c r="L284" s="61"/>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A285" s="47" t="s">
+      <c r="L284" s="6"/>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A285" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="B285" s="48"/>
-      <c r="C285" s="49"/>
-      <c r="D285" s="70"/>
-      <c r="E285" s="71" t="s">
+      <c r="C285" s="47"/>
+      <c r="D285" s="15"/>
+      <c r="E285" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="F285" s="72"/>
-      <c r="L285" s="61"/>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A286" s="47" t="s">
+      <c r="L285" s="6"/>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A286" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B286" s="48"/>
-      <c r="C286" s="49"/>
+      <c r="C286" s="47"/>
       <c r="D286" s="15"/>
-      <c r="L286" s="61"/>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A287" s="47" t="s">
+      <c r="L286" s="6"/>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A287" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B287" s="48"/>
-      <c r="C287" s="49"/>
+      <c r="C287" s="47"/>
       <c r="D287" s="15"/>
-      <c r="E287" s="61"/>
-      <c r="L287" s="61"/>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A288" s="47" t="s">
+      <c r="E287" s="6"/>
+      <c r="L287" s="6"/>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A288" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B288" s="48"/>
-      <c r="C288" s="49"/>
+      <c r="C288" s="47"/>
       <c r="D288" s="15"/>
-      <c r="L288" s="61"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A289" s="50" t="s">
+      <c r="L288" s="6"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="B289" s="59"/>
-      <c r="C289" s="60"/>
+      <c r="B289" s="55"/>
+      <c r="C289" s="56"/>
       <c r="D289" s="16"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A292" s="25" t="s">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A294" s="44" t="s">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="B294" s="45"/>
-      <c r="C294" s="45"/>
-      <c r="D294" s="45"/>
-      <c r="E294" s="33"/>
-      <c r="F294" s="53" t="s">
+      <c r="B294" s="44"/>
+      <c r="C294" s="44"/>
+      <c r="D294" s="44"/>
+      <c r="E294" s="32"/>
+      <c r="F294" s="51" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A295" s="47" t="s">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="B295" s="48"/>
-      <c r="C295" s="48"/>
-      <c r="D295" s="48"/>
-      <c r="E295" s="39"/>
-      <c r="F295" s="53"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A296" s="47" t="s">
+      <c r="E295" s="38"/>
+      <c r="F295" s="51"/>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="B296" s="48"/>
-      <c r="C296" s="48"/>
-      <c r="D296" s="48"/>
-      <c r="E296" s="39"/>
-      <c r="F296" s="53"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A297" s="50" t="s">
+      <c r="E296" s="38"/>
+      <c r="F296" s="51"/>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B297" s="59"/>
-      <c r="C297" s="59"/>
-      <c r="D297" s="59"/>
-      <c r="E297" s="36"/>
-      <c r="F297" s="53" t="s">
+      <c r="B297" s="55"/>
+      <c r="C297" s="55"/>
+      <c r="D297" s="55"/>
+      <c r="E297" s="35"/>
+      <c r="F297" s="51" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A300" s="30" t="s">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="B300" s="29" t="s">
+      <c r="B300" s="28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A301" s="30" t="s">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="B301" s="29"/>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A302" s="30"/>
-      <c r="B302" s="29"/>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A303" s="30" t="s">
+      <c r="B301" s="28"/>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A302" s="29"/>
+      <c r="B302" s="28"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A303" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="B303" s="29" t="s">
+      <c r="B303" s="28" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A304" s="30" t="s">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="B304" s="29"/>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B305" s="29"/>
+      <c r="B304" s="28"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B305" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5228,22 +5144,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6EF22B-F0D0-437F-83DE-19364E73AE25}">
   <dimension ref="A1:AE305"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>0</v>
@@ -5257,7 +5173,7 @@
       <c r="E6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="3" t="s">
         <v>168</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -5315,7 +5231,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -5323,7 +5239,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="66"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="4"/>
       <c r="I7" s="3">
@@ -5359,7 +5275,7 @@
         <v>6083.9481150695065</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>1</v>
       </c>
@@ -5367,7 +5283,7 @@
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="67"/>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
       <c r="I8" s="6">
@@ -5403,7 +5319,7 @@
         <v>530.99793367786128</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
@@ -5411,7 +5327,7 @@
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="67"/>
+      <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="7"/>
       <c r="I9" s="6">
@@ -5447,7 +5363,7 @@
         <v>11592.41657869403</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>3</v>
       </c>
@@ -5455,7 +5371,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="67"/>
+      <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="7"/>
       <c r="I10" s="6">
@@ -5491,7 +5407,7 @@
         <v>4964.714367304332</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>168</v>
       </c>
@@ -5499,7 +5415,7 @@
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
-      <c r="F11" s="67"/>
+      <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="7"/>
       <c r="I11" s="6">
@@ -5535,7 +5451,7 @@
         <v>4949.2697196303889</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>4</v>
       </c>
@@ -5543,7 +5459,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="67"/>
+      <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="7"/>
       <c r="I12" s="6">
@@ -5579,7 +5495,7 @@
         <v>2262.4772704116963</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>184</v>
       </c>
@@ -5587,7 +5503,7 @@
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="67"/>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="7"/>
       <c r="I13" s="6">
@@ -5623,7 +5539,7 @@
         <v>5637.3176678953205</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -5639,7 +5555,7 @@
       <c r="E14" s="3">
         <v>218.84704685761815</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
@@ -5676,14 +5592,14 @@
       <c r="X14" s="4">
         <v>6428.5703532211328</v>
       </c>
-      <c r="Z14" s="61"/>
-      <c r="AA14" s="61"/>
-      <c r="AB14" s="61"/>
-      <c r="AC14" s="61"/>
-      <c r="AD14" s="61"/>
-      <c r="AE14" s="61"/>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -5699,7 +5615,7 @@
       <c r="E15" s="6">
         <v>314.27975862244585</v>
       </c>
-      <c r="F15" s="67">
+      <c r="F15" s="6">
         <v>88.758563717962957</v>
       </c>
       <c r="G15" s="6">
@@ -5737,7 +5653,7 @@
         <v>634.83870384962336</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
@@ -5753,7 +5669,7 @@
       <c r="E16" s="6">
         <v>1805.2238927827259</v>
       </c>
-      <c r="F16" s="67">
+      <c r="F16" s="6">
         <v>526.72555085137151</v>
       </c>
       <c r="G16" s="6">
@@ -5791,7 +5707,7 @@
         <v>15149.928070463553</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>8</v>
       </c>
@@ -5807,7 +5723,7 @@
       <c r="E17" s="6">
         <v>374.85065844644004</v>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="6">
         <v>49.087495294874827</v>
       </c>
       <c r="G17" s="6">
@@ -5845,7 +5761,7 @@
         <v>4981.8058560754589</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>167</v>
       </c>
@@ -5861,7 +5777,7 @@
       <c r="E18" s="6">
         <v>104.53241537752901</v>
       </c>
-      <c r="F18" s="67">
+      <c r="F18" s="6">
         <v>76.088551577062759</v>
       </c>
       <c r="G18" s="6">
@@ -5899,7 +5815,7 @@
         <v>5378.5714066022902</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>9</v>
       </c>
@@ -5915,7 +5831,7 @@
       <c r="E19" s="6">
         <v>36.361870747235798</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="6">
         <v>33.664324915703766</v>
       </c>
       <c r="G19" s="6">
@@ -5953,7 +5869,7 @@
         <v>2277.9121662753387</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>185</v>
       </c>
@@ -5969,7 +5885,7 @@
       <c r="E20" s="9">
         <v>617.38674573713388</v>
       </c>
-      <c r="F20" s="68">
+      <c r="F20" s="9">
         <v>500.0888416258033</v>
       </c>
       <c r="G20" s="9">
@@ -6007,7 +5923,7 @@
         <v>5779.0603770187263</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>10</v>
       </c>
@@ -6023,7 +5939,7 @@
       <c r="E21" s="6">
         <v>1054.5939496360331</v>
       </c>
-      <c r="F21" s="67">
+      <c r="F21" s="6">
         <v>670.35889402609632</v>
       </c>
       <c r="G21" s="6">
@@ -6053,7 +5969,7 @@
         <v>6079.4216885859878</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>11</v>
       </c>
@@ -6069,7 +5985,7 @@
       <c r="E22" s="6">
         <v>438.63802909716787</v>
       </c>
-      <c r="F22" s="67">
+      <c r="F22" s="6">
         <v>3004.4974976215126</v>
       </c>
       <c r="G22" s="6">
@@ -6099,7 +6015,7 @@
         <v>10181.806872848019</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
         <v>188</v>
       </c>
@@ -6107,7 +6023,7 @@
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
-      <c r="F23" s="69"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="12"/>
@@ -6141,7 +6057,7 @@
         <v>10189.884565311602</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -6149,7 +6065,7 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="66"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="4"/>
       <c r="I24" s="3"/>
@@ -6185,7 +6101,7 @@
         <v>8616.6805824517432</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
@@ -6193,7 +6109,7 @@
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="68"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="10"/>
       <c r="I25" s="9"/>
@@ -6229,7 +6145,7 @@
         <v>5775.3997392920746</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
@@ -6245,7 +6161,7 @@
       <c r="E26" s="6">
         <v>0</v>
       </c>
-      <c r="F26" s="67">
+      <c r="F26" s="6">
         <v>0</v>
       </c>
       <c r="G26" s="6">
@@ -6299,7 +6215,7 @@
         <v>1634.0800405341656</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>15</v>
       </c>
@@ -6307,7 +6223,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="67"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="7"/>
       <c r="I27" s="6"/>
@@ -6339,7 +6255,7 @@
         <v>5218.0019059164133</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>16</v>
       </c>
@@ -6347,7 +6263,7 @@
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="67"/>
+      <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="7"/>
       <c r="I28" s="6">
@@ -6395,7 +6311,7 @@
         <v>3992.5392070432972</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
         <v>17</v>
       </c>
@@ -6411,7 +6327,7 @@
       <c r="E29" s="12">
         <v>4964.7143673043302</v>
       </c>
-      <c r="F29" s="69">
+      <c r="F29" s="12">
         <v>4949.269719630388</v>
       </c>
       <c r="G29" s="12">
@@ -6467,42 +6383,42 @@
       </c>
       <c r="X29" s="17"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="63"/>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="R30" s="64"/>
-      <c r="S30" s="64"/>
-      <c r="T30" s="64"/>
-      <c r="U30" s="64"/>
-    </row>
-    <row r="31" spans="1:24" ht="18" x14ac:dyDescent="0.35">
-      <c r="A31" s="40" t="s">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A30" s="58"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="59"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="59"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="59"/>
+      <c r="T30" s="59"/>
+      <c r="U30" s="59"/>
+    </row>
+    <row r="31" spans="1:24" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" s="24" t="s">
         <v>39</v>
       </c>
       <c r="Q33" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -6513,16 +6429,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B35" s="90" t="s">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="B35" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="91"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="92"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="79"/>
       <c r="Q35" t="s">
         <v>1</v>
       </c>
@@ -6530,7 +6446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B36" s="2" t="s">
         <v>0</v>
       </c>
@@ -6562,7 +6478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
         <v>5</v>
       </c>
@@ -6605,8 +6521,8 @@
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="47" t="s">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A38" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="6">
@@ -6648,7 +6564,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="21" t="s">
         <v>7</v>
       </c>
@@ -6691,7 +6607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="21" t="s">
         <v>8</v>
       </c>
@@ -6734,7 +6650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="21" t="s">
         <v>167</v>
       </c>
@@ -6777,7 +6693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="21" t="s">
         <v>9</v>
       </c>
@@ -6820,7 +6736,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
         <v>185</v>
       </c>
@@ -6863,7 +6779,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
         <v>10</v>
       </c>
@@ -6906,7 +6822,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
         <v>11</v>
       </c>
@@ -6949,7 +6865,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
         <v>17</v>
       </c>
@@ -6985,7 +6901,7 @@
         <f>SUM(B46:H46)</f>
         <v>36021.141652683138</v>
       </c>
-      <c r="J46" s="51">
+      <c r="J46" s="49">
         <v>36021.141652683138</v>
       </c>
       <c r="Q46" t="s">
@@ -6995,7 +6911,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q47" t="s">
         <v>185</v>
       </c>
@@ -7003,7 +6919,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q48" t="s">
         <v>10</v>
       </c>
@@ -7011,8 +6927,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A49" s="25" t="s">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A49" s="24" t="s">
         <v>41</v>
       </c>
       <c r="Q49" t="s">
@@ -7022,7 +6938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -7033,7 +6949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B51" s="2" t="s">
         <v>0</v>
       </c>
@@ -7065,8 +6981,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A52" s="23" t="s">
         <v>42</v>
       </c>
       <c r="B52" s="12">
@@ -7101,7 +7017,7 @@
         <f>SUM(B52:H52)</f>
         <v>16253.845987905948</v>
       </c>
-      <c r="J52" s="51">
+      <c r="J52" s="49">
         <v>16253.845987905948</v>
       </c>
       <c r="Q52" t="s">
@@ -7111,7 +7027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q53" t="s">
         <v>15</v>
       </c>
@@ -7119,7 +7035,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q54" t="s">
         <v>16</v>
       </c>
@@ -7127,18 +7043,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A55" s="25" t="s">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A55" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
+      <c r="B55" s="24"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
       <c r="Q55" t="s">
         <v>17</v>
       </c>
@@ -7146,12 +7062,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B57" s="2" t="s">
         <v>0</v>
       </c>
@@ -7177,76 +7093,76 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A58" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="74">
+      <c r="B58" s="61">
         <f>B52/$I$52*100</f>
         <v>16.287266015307729</v>
       </c>
-      <c r="C58" s="74">
+      <c r="C58" s="61">
         <f t="shared" ref="C58:H58" si="5">C52/$I$52*100</f>
         <v>1.7575251844885342</v>
       </c>
-      <c r="D58" s="74">
+      <c r="D58" s="61">
         <f t="shared" si="5"/>
         <v>17.1472425473059</v>
       </c>
-      <c r="E58" s="74">
+      <c r="E58" s="61">
         <f t="shared" si="5"/>
         <v>9.1869455379623677</v>
       </c>
-      <c r="F58" s="74">
+      <c r="F58" s="61">
         <f t="shared" si="5"/>
         <v>22.60914982449059</v>
       </c>
-      <c r="G58" s="74">
+      <c r="G58" s="61">
         <f t="shared" si="5"/>
         <v>9.0816053578207327</v>
       </c>
-      <c r="H58" s="74">
+      <c r="H58" s="61">
         <f t="shared" si="5"/>
         <v>23.930265532624151</v>
       </c>
-      <c r="I58" s="75">
+      <c r="I58" s="62">
         <f>SUM(B58:H58)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="H59" s="52">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="H59" s="50">
         <v>23.930265532624151</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A61" s="30" t="s">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A61" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A62" s="30" t="s">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A62" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="B62" s="62">
+      <c r="B62" s="57">
         <f>C58/100</f>
         <v>1.7575251844885342E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="25" t="s">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" s="24" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B67" s="2" t="s">
         <v>0</v>
       </c>
@@ -7272,210 +7188,210 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B68" s="76">
+      <c r="B68" s="63">
         <f>B44/B$52*100</f>
         <v>65.715774110046851</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="63">
         <f t="shared" ref="C68:I68" si="6">C44/C$52*100</f>
         <v>18.611318121044476</v>
       </c>
-      <c r="D68" s="76">
+      <c r="D68" s="63">
         <f t="shared" si="6"/>
         <v>42.461344516305658</v>
       </c>
-      <c r="E68" s="76">
+      <c r="E68" s="63">
         <f t="shared" si="6"/>
         <v>70.624923967320129</v>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="63">
         <f t="shared" si="6"/>
         <v>18.241771176411696</v>
       </c>
-      <c r="G68" s="76">
+      <c r="G68" s="63">
         <f t="shared" si="6"/>
         <v>66.051036427997374</v>
       </c>
-      <c r="H68" s="76">
+      <c r="H68" s="63">
         <f t="shared" si="6"/>
         <v>10.314699400110754</v>
       </c>
-      <c r="I68" s="77">
+      <c r="I68" s="64">
         <f t="shared" si="6"/>
         <v>37.39076337502312</v>
       </c>
-      <c r="J68" s="52">
+      <c r="J68" s="50">
         <v>37.39076337502312</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="78">
+      <c r="B69" s="65">
         <f t="shared" ref="B69:I69" si="7">B45/B$52*100</f>
         <v>34.284225889953142</v>
       </c>
-      <c r="C69" s="78">
+      <c r="C69" s="65">
         <f t="shared" si="7"/>
         <v>81.388681878955524</v>
       </c>
-      <c r="D69" s="78">
+      <c r="D69" s="65">
         <f t="shared" si="7"/>
         <v>57.538655483694342</v>
       </c>
-      <c r="E69" s="78">
+      <c r="E69" s="65">
         <f t="shared" si="7"/>
         <v>29.375076032679871</v>
       </c>
-      <c r="F69" s="78">
+      <c r="F69" s="65">
         <f t="shared" si="7"/>
         <v>81.758228823588311</v>
       </c>
-      <c r="G69" s="78">
+      <c r="G69" s="65">
         <f t="shared" si="7"/>
         <v>33.948963572002619</v>
       </c>
-      <c r="H69" s="78">
+      <c r="H69" s="65">
         <f t="shared" si="7"/>
         <v>89.685300599889246</v>
       </c>
-      <c r="I69" s="79">
+      <c r="I69" s="66">
         <f t="shared" si="7"/>
         <v>62.609236624976894</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B70" s="78">
+      <c r="B70" s="65">
         <f>SUM(B68:B69)</f>
         <v>100</v>
       </c>
-      <c r="C70" s="78">
+      <c r="C70" s="65">
         <f t="shared" ref="C70:I70" si="8">SUM(C68:C69)</f>
         <v>100</v>
       </c>
-      <c r="D70" s="78">
+      <c r="D70" s="65">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="E70" s="78">
+      <c r="E70" s="65">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="F70" s="78">
+      <c r="F70" s="65">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="G70" s="78">
+      <c r="G70" s="65">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="H70" s="78">
+      <c r="H70" s="65">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="I70" s="79">
+      <c r="I70" s="66">
         <f t="shared" si="8"/>
         <v>100.00000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="30" t="s">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B73" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="29"/>
-      <c r="I73" s="29"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="30" t="s">
+      <c r="C73" s="28"/>
+      <c r="D73" s="28"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B74" s="29" t="s">
+      <c r="B74" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="29"/>
-      <c r="I74" s="29"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="30"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="30" t="s">
+      <c r="C74" s="28"/>
+      <c r="D74" s="28"/>
+      <c r="E74" s="28"/>
+      <c r="F74" s="28"/>
+      <c r="G74" s="28"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="28"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="29"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="28"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" s="30" t="s">
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="28"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="B77" s="29" t="s">
+      <c r="B77" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" s="25" t="s">
+      <c r="C77" s="28"/>
+      <c r="D77" s="28"/>
+      <c r="E77" s="28"/>
+      <c r="F77" s="28"/>
+      <c r="G77" s="28"/>
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25"/>
-      <c r="I80" s="25"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24"/>
+      <c r="I80" s="24"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B82" s="2" t="s">
         <v>0</v>
       </c>
@@ -7501,444 +7417,444 @@
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B83" s="54">
+      <c r="B83" s="52">
         <f>B37/B$46*100</f>
         <v>15.357745633006667</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="30">
         <f t="shared" ref="C83:H83" si="9">C37/C$46*100</f>
         <v>0</v>
       </c>
-      <c r="D83" s="31">
+      <c r="D83" s="30">
         <f t="shared" si="9"/>
         <v>12.87178175415634</v>
       </c>
-      <c r="E83" s="31">
+      <c r="E83" s="30">
         <f t="shared" si="9"/>
         <v>4.4080490974235973</v>
       </c>
-      <c r="F83" s="31">
+      <c r="F83" s="30">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="G83" s="31">
+      <c r="G83" s="30">
         <f t="shared" si="9"/>
         <v>0.63469670911753484</v>
       </c>
-      <c r="H83" s="31">
+      <c r="H83" s="30">
         <f t="shared" si="9"/>
         <v>3.5670027102659358</v>
       </c>
-      <c r="I83" s="33">
+      <c r="I83" s="32">
         <f t="shared" ref="I83" si="10">I37/I$46*100</f>
         <v>7.9419971060886576</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="55">
+      <c r="B84" s="53">
         <f t="shared" ref="B84:H84" si="11">B38/B$46*100</f>
         <v>0.21890853390875645</v>
       </c>
-      <c r="C84" s="37">
+      <c r="C84" s="36">
         <f t="shared" si="11"/>
         <v>1.8698612604864904</v>
       </c>
-      <c r="D84" s="37">
+      <c r="D84" s="36">
         <f t="shared" si="11"/>
         <v>1.6493978912162131</v>
       </c>
-      <c r="E84" s="37">
+      <c r="E84" s="36">
         <f t="shared" si="11"/>
         <v>6.3302686795471974</v>
       </c>
-      <c r="F84" s="37">
+      <c r="F84" s="36">
         <f t="shared" si="11"/>
         <v>1.7933668752365239</v>
       </c>
-      <c r="G84" s="37">
+      <c r="G84" s="36">
         <f t="shared" si="11"/>
         <v>7.6461907769365999E-3</v>
       </c>
-      <c r="H84" s="37">
+      <c r="H84" s="36">
         <f t="shared" si="11"/>
         <v>0.27755515556553895</v>
       </c>
-      <c r="I84" s="39">
+      <c r="I84" s="38">
         <f t="shared" ref="I84" si="12">I38/I$46*100</f>
         <v>1.7581626603240597</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B85" s="55">
+      <c r="B85" s="53">
         <f t="shared" ref="B85:H85" si="13">B39/B$46*100</f>
         <v>7.9584001868790999</v>
       </c>
-      <c r="C85" s="37">
+      <c r="C85" s="36">
         <f t="shared" si="13"/>
         <v>17.466516254152044</v>
       </c>
-      <c r="D85" s="37">
+      <c r="D85" s="36">
         <f t="shared" si="13"/>
         <v>26.056720184346876</v>
       </c>
-      <c r="E85" s="37">
+      <c r="E85" s="36">
         <f t="shared" si="13"/>
         <v>36.361082616781047</v>
       </c>
-      <c r="F85" s="37">
+      <c r="F85" s="36">
         <f t="shared" si="13"/>
         <v>10.642490320586274</v>
       </c>
-      <c r="G85" s="37">
+      <c r="G85" s="36">
         <f t="shared" si="13"/>
         <v>21.177416922888181</v>
       </c>
-      <c r="H85" s="37">
+      <c r="H85" s="36">
         <f t="shared" si="13"/>
         <v>10.528867296064618</v>
       </c>
-      <c r="I85" s="39">
+      <c r="I85" s="38">
         <f t="shared" ref="I85" si="14">I39/I$46*100</f>
         <v>19.439041607477769</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B86" s="55">
+      <c r="B86" s="53">
         <f t="shared" ref="B86:H86" si="15">B40/B$46*100</f>
         <v>4.5342196279408005E-2</v>
       </c>
-      <c r="C86" s="37">
+      <c r="C86" s="36">
         <f t="shared" si="15"/>
         <v>0.88048077632544475</v>
       </c>
-      <c r="D86" s="37">
+      <c r="D86" s="36">
         <f t="shared" si="15"/>
         <v>2.8077280527923039</v>
       </c>
-      <c r="E86" s="37">
+      <c r="E86" s="36">
         <f t="shared" si="15"/>
         <v>7.5502965672116025</v>
       </c>
-      <c r="F86" s="37">
+      <c r="F86" s="36">
         <f t="shared" si="15"/>
         <v>0.99181289514649229</v>
       </c>
-      <c r="G86" s="37">
+      <c r="G86" s="36">
         <f t="shared" si="15"/>
         <v>0.32380235146733055</v>
       </c>
-      <c r="H86" s="37">
+      <c r="H86" s="36">
         <f t="shared" si="15"/>
         <v>0.78748081509600731</v>
       </c>
-      <c r="I86" s="39">
+      <c r="I86" s="38">
         <f t="shared" ref="I86" si="16">I40/I$46*100</f>
         <v>2.2447216525296203</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="55">
+      <c r="B87" s="53">
         <f t="shared" ref="B87:H87" si="17">B41/B$46*100</f>
         <v>30.658049043270612</v>
       </c>
-      <c r="C87" s="37">
+      <c r="C87" s="36">
         <f t="shared" si="17"/>
         <v>3.1185827540468187</v>
       </c>
-      <c r="D87" s="37">
+      <c r="D87" s="36">
         <f t="shared" si="17"/>
         <v>23.186257471163216</v>
       </c>
-      <c r="E87" s="37">
+      <c r="E87" s="36">
         <f t="shared" si="17"/>
         <v>2.1055071378514474</v>
       </c>
-      <c r="F87" s="37">
+      <c r="F87" s="36">
         <f t="shared" si="17"/>
         <v>1.5373692663237004</v>
       </c>
-      <c r="G87" s="37">
+      <c r="G87" s="36">
         <f t="shared" si="17"/>
         <v>1.8986270469979856</v>
       </c>
-      <c r="H87" s="37">
+      <c r="H87" s="36">
         <f t="shared" si="17"/>
         <v>1.6016787408612843</v>
       </c>
-      <c r="I87" s="39">
+      <c r="I87" s="38">
         <f t="shared" ref="I87" si="18">I41/I$46*100</f>
         <v>13.557303930025553</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="55">
+      <c r="B88" s="53">
         <f t="shared" ref="B88:H88" si="19">B42/B$46*100</f>
         <v>1.0119650972105951</v>
       </c>
-      <c r="C88" s="37">
+      <c r="C88" s="36">
         <f t="shared" si="19"/>
         <v>2.4268395578084254</v>
       </c>
-      <c r="D88" s="37">
+      <c r="D88" s="36">
         <f t="shared" si="19"/>
         <v>0.56911006924570207</v>
       </c>
-      <c r="E88" s="37">
+      <c r="E88" s="36">
         <f t="shared" si="19"/>
         <v>0.73240609745247143</v>
       </c>
-      <c r="F88" s="37">
+      <c r="F88" s="36">
         <f t="shared" si="19"/>
         <v>0.68018772107287417</v>
       </c>
-      <c r="G88" s="37">
+      <c r="G88" s="36">
         <f t="shared" si="19"/>
         <v>6.0349086936346525</v>
       </c>
-      <c r="H88" s="37">
+      <c r="H88" s="36">
         <f t="shared" si="19"/>
         <v>0.64676330087600964</v>
       </c>
-      <c r="I88" s="39">
+      <c r="I88" s="38">
         <f t="shared" ref="I88" si="20">I42/I$46*100</f>
         <v>1.0645199645650532</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B89" s="73">
+      <c r="B89" s="60">
         <f t="shared" ref="B89:H89" si="21">B43/B$46*100</f>
         <v>1.2366091903101444</v>
       </c>
-      <c r="C89" s="34">
+      <c r="C89" s="33">
         <f t="shared" si="21"/>
         <v>20.439876022006757</v>
       </c>
-      <c r="D89" s="34">
+      <c r="D89" s="33">
         <f t="shared" si="21"/>
         <v>8.8166802188067841</v>
       </c>
-      <c r="E89" s="34">
+      <c r="E89" s="33">
         <f t="shared" si="21"/>
         <v>12.435493767838929</v>
       </c>
-      <c r="F89" s="34">
+      <c r="F89" s="33">
         <f t="shared" si="21"/>
         <v>10.104295582079329</v>
       </c>
-      <c r="G89" s="34">
+      <c r="G89" s="33">
         <f t="shared" si="21"/>
         <v>4.6798091535807744</v>
       </c>
-      <c r="H89" s="34">
+      <c r="H89" s="33">
         <f t="shared" si="21"/>
         <v>13.593502391475692</v>
       </c>
-      <c r="I89" s="36">
+      <c r="I89" s="35">
         <f t="shared" ref="I89" si="22">I43/I$46*100</f>
         <v>8.8711802329756875</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B90" s="54">
+      <c r="B90" s="52">
         <f t="shared" ref="B90:H90" si="23">B44/B$46*100</f>
         <v>28.594891723640163</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="30">
         <f t="shared" si="23"/>
         <v>10.012487772814888</v>
       </c>
-      <c r="D90" s="31">
+      <c r="D90" s="30">
         <f t="shared" si="23"/>
         <v>10.208694175493784</v>
       </c>
-      <c r="E90" s="31">
+      <c r="E90" s="30">
         <f t="shared" si="23"/>
         <v>21.241784957079847</v>
       </c>
-      <c r="F90" s="31">
+      <c r="F90" s="30">
         <f t="shared" si="23"/>
         <v>13.544602173675004</v>
       </c>
-      <c r="G90" s="31">
+      <c r="G90" s="30">
         <f t="shared" si="23"/>
         <v>43.09373907896142</v>
       </c>
-      <c r="H90" s="31">
+      <c r="H90" s="30">
         <f t="shared" si="23"/>
         <v>7.1168485748320949</v>
       </c>
-      <c r="I90" s="33">
+      <c r="I90" s="32">
         <f t="shared" ref="I90" si="24">I44/I$46*100</f>
         <v>16.871861395392244</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="73">
+      <c r="B91" s="60">
         <f t="shared" ref="B91:H91" si="25">B45/B$46*100</f>
         <v>14.918088395494546</v>
       </c>
-      <c r="C91" s="34">
+      <c r="C91" s="33">
         <f t="shared" si="25"/>
         <v>43.785355602359132</v>
       </c>
-      <c r="D91" s="34">
+      <c r="D91" s="33">
         <f t="shared" si="25"/>
         <v>13.833630182778778</v>
       </c>
-      <c r="E91" s="34">
+      <c r="E91" s="33">
         <f t="shared" si="25"/>
         <v>8.8351110788138509</v>
       </c>
-      <c r="F91" s="34">
+      <c r="F91" s="33">
         <f t="shared" si="25"/>
         <v>60.705875165879796</v>
       </c>
-      <c r="G91" s="34">
+      <c r="G91" s="33">
         <f t="shared" si="25"/>
         <v>22.149353852575171</v>
       </c>
-      <c r="H91" s="34">
+      <c r="H91" s="33">
         <f t="shared" si="25"/>
         <v>61.880301014962811</v>
       </c>
-      <c r="I91" s="36">
+      <c r="I91" s="35">
         <f t="shared" ref="I91" si="26">I45/I$46*100</f>
         <v>28.251211450621334</v>
       </c>
-      <c r="J91" s="52">
+      <c r="J91" s="50">
         <v>28.251211450621334</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B92" s="73">
+      <c r="B92" s="60">
         <f t="shared" ref="B92:H92" si="27">B46/B$46*100</f>
         <v>100</v>
       </c>
-      <c r="C92" s="26">
+      <c r="C92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="D92" s="26">
+      <c r="D92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="E92" s="26">
+      <c r="E92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="F92" s="26">
+      <c r="F92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="G92" s="26">
+      <c r="G92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="H92" s="26">
+      <c r="H92" s="25">
         <f t="shared" si="27"/>
         <v>100</v>
       </c>
-      <c r="I92" s="28">
+      <c r="I92" s="27">
         <f t="shared" ref="I92" si="28">I46/I$46*100</f>
         <v>100</v>
       </c>
-      <c r="J92" s="52">
+      <c r="J92" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A95" s="30" t="s">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B95" s="29" t="s">
+      <c r="B95" s="28" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A96" s="30" t="s">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="B96" s="62">
+      <c r="B96" s="57">
         <f>B85/100</f>
         <v>7.9584001868790999E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A97" s="30"/>
-      <c r="B97" s="29"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A98" s="30" t="s">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" s="29"/>
+      <c r="B97" s="28"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B98" s="29" t="s">
+      <c r="B98" s="28" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A99" s="30" t="s">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B99" s="80">
+      <c r="B99" s="67">
         <f>F87/100</f>
         <v>1.5373692663237005E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18" x14ac:dyDescent="0.35">
-      <c r="A102" s="40" t="s">
+    <row r="102" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A102" s="39" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A104" s="25" t="s">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A104" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="B104" s="25"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25"/>
-      <c r="G104" s="25"/>
-      <c r="H104" s="25"/>
-      <c r="I104" s="25"/>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B104" s="24"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="24"/>
+      <c r="I104" s="24"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B106" s="2" t="s">
         <v>5</v>
       </c>
@@ -7964,7 +7880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="20" t="s">
         <v>62</v>
       </c>
@@ -7992,9 +7908,9 @@
       <c r="I107" s="14">
         <v>3749.0182620505557</v>
       </c>
-      <c r="J107" s="51"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J107" s="49"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="22" t="s">
         <v>63</v>
       </c>
@@ -8022,29 +7938,29 @@
       <c r="I108" s="16">
         <v>3263.3659055205276</v>
       </c>
-      <c r="J108" s="51">
+      <c r="J108" s="49">
         <v>3263.3659055205276</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A111" s="25" t="s">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A111" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
-      <c r="I111" s="25"/>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B111" s="24"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="24"/>
+      <c r="H111" s="24"/>
+      <c r="I111" s="24"/>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B113" s="2" t="s">
         <v>5</v>
       </c>
@@ -8070,167 +7986,167 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B114" s="54">
+      <c r="B114" s="52">
         <f>B107/$I107*100</f>
         <v>8.7706325354188781</v>
       </c>
-      <c r="C114" s="31">
+      <c r="C114" s="30">
         <f t="shared" ref="C114:I114" si="29">C107/$I107*100</f>
         <v>2.5008051370975037</v>
       </c>
-      <c r="D114" s="31">
+      <c r="D114" s="30">
         <f t="shared" si="29"/>
         <v>72.629126727510155</v>
       </c>
-      <c r="E114" s="31">
+      <c r="E114" s="30">
         <f t="shared" si="29"/>
         <v>0.45589238505812457</v>
       </c>
-      <c r="F114" s="31">
+      <c r="F114" s="30">
         <f t="shared" si="29"/>
         <v>11.451042832133066</v>
       </c>
-      <c r="G114" s="31">
+      <c r="G114" s="30">
         <f t="shared" si="29"/>
         <v>0.41170500607804639</v>
       </c>
-      <c r="H114" s="32">
+      <c r="H114" s="31">
         <f t="shared" si="29"/>
         <v>3.7807953767042255</v>
       </c>
-      <c r="I114" s="33">
+      <c r="I114" s="32">
         <f t="shared" si="29"/>
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B115" s="73">
+      <c r="B115" s="60">
         <f t="shared" ref="B115:I115" si="30">B108/$I108*100</f>
         <v>0.83766987385998548</v>
       </c>
-      <c r="C115" s="34">
+      <c r="C115" s="33">
         <f t="shared" si="30"/>
         <v>4.6836350380629381E-2</v>
       </c>
-      <c r="D115" s="34">
+      <c r="D115" s="33">
         <f t="shared" si="30"/>
         <v>91.151489857083035</v>
       </c>
-      <c r="E115" s="34">
+      <c r="E115" s="33">
         <f t="shared" si="30"/>
         <v>0.25370605358418596</v>
       </c>
-      <c r="F115" s="34">
+      <c r="F115" s="33">
         <f t="shared" si="30"/>
         <v>0.98686383365391794</v>
       </c>
-      <c r="G115" s="34">
+      <c r="G115" s="33">
         <f t="shared" si="30"/>
         <v>3.4896390755981757</v>
       </c>
-      <c r="H115" s="35">
+      <c r="H115" s="34">
         <f t="shared" si="30"/>
         <v>3.2337949558400831</v>
       </c>
-      <c r="I115" s="36">
+      <c r="I115" s="35">
         <f t="shared" si="30"/>
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H116" s="52">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H116" s="50">
         <v>3.2337949558400831</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="30" t="s">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A118" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B118" s="29" t="s">
+      <c r="B118" s="28" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="30" t="s">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A119" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B119" s="29" t="s">
+      <c r="B119" s="28" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="30"/>
-      <c r="B120" s="29"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="30" t="s">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A120" s="29"/>
+      <c r="B120" s="28"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A121" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="B121" s="29" t="s">
+      <c r="B121" s="28" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="30" t="s">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A122" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="B122" s="29" t="s">
+      <c r="B122" s="28" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A125" s="25" t="s">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A125" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B125" s="25"/>
-      <c r="C125" s="25"/>
-      <c r="D125" s="25"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25"/>
-      <c r="G125" s="25"/>
-      <c r="H125" s="25"/>
-      <c r="I125" s="25"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B125" s="24"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+      <c r="H125" s="24"/>
+      <c r="I125" s="24"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B127" s="41" t="s">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B127" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="42" t="s">
+      <c r="C127" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D127" s="42" t="s">
+      <c r="D127" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="E127" s="42" t="s">
+      <c r="E127" s="41" t="s">
         <v>8</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G127" s="42" t="s">
+      <c r="G127" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H127" s="43" t="s">
+      <c r="H127" s="42" t="s">
         <v>185</v>
       </c>
-      <c r="I127" s="43" t="s">
+      <c r="I127" s="42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A128" s="44" t="s">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A128" s="43" t="s">
         <v>78</v>
       </c>
       <c r="B128" s="2">
@@ -8259,15 +8175,15 @@
         <f>SUM(B128:H128)</f>
         <v>40630.68693350612</v>
       </c>
-      <c r="J128" s="51">
+      <c r="J128" s="49">
         <v>13700.655862697891</v>
       </c>
-      <c r="K128" s="53" t="s">
+      <c r="K128" s="51" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A129" s="47" t="s">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A129" s="46" t="s">
         <v>79</v>
       </c>
       <c r="B129" s="5">
@@ -8278,19 +8194,19 @@
         <f>SUM(B15:H15)</f>
         <v>633.3102623599118</v>
       </c>
-      <c r="D129" s="61">
+      <c r="D129" s="6">
         <f>SUM(B16:H16)</f>
         <v>7002.1647133535807</v>
       </c>
-      <c r="E129" s="61">
+      <c r="E129" s="6">
         <f>SUM(B17:H17)</f>
         <v>808.57436616614427</v>
       </c>
-      <c r="F129" s="61">
+      <c r="F129" s="6">
         <f>SUM(B18:H18)</f>
         <v>4883.4956529192823</v>
       </c>
-      <c r="G129" s="61">
+      <c r="G129" s="6">
         <f>SUM(B19:H19)</f>
         <v>383.45224435707019</v>
       </c>
@@ -8302,16 +8218,16 @@
         <f t="shared" ref="I129:I130" si="31">SUM(B129:H129)</f>
         <v>19767.295664777179</v>
       </c>
-      <c r="J129" s="51">
+      <c r="J129" s="49">
         <v>5876.6053797057857</v>
       </c>
-      <c r="K129" s="53" t="s">
+      <c r="K129" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="V129" s="61"/>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A130" s="50" t="s">
+      <c r="V129" s="6"/>
+    </row>
+    <row r="130" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A130" s="48" t="s">
         <v>80</v>
       </c>
       <c r="B130" s="8">
@@ -8346,33 +8262,33 @@
         <f t="shared" si="31"/>
         <v>20863.391268728945</v>
       </c>
-      <c r="K130" s="53" t="s">
+      <c r="K130" s="51" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="H131" s="51">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="H131" s="49">
         <v>2583.5599790337283</v>
       </c>
-      <c r="K131" s="53"/>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="K132" s="53"/>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A133" s="25" t="s">
+      <c r="K131" s="51"/>
+    </row>
+    <row r="132" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="K132" s="51"/>
+    </row>
+    <row r="133" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A133" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="K133" s="53"/>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="K133" s="51"/>
+    </row>
+    <row r="134" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>82</v>
       </c>
-      <c r="K134" s="53"/>
-      <c r="V134" s="61"/>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="K134" s="51"/>
+      <c r="V134" s="6"/>
+    </row>
+    <row r="135" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B135" s="2" t="s">
         <v>5</v>
       </c>
@@ -8397,188 +8313,188 @@
       <c r="I135" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="K135" s="53"/>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="K135" s="51"/>
+    </row>
+    <row r="136" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A136" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B136" s="31">
+      <c r="B136" s="30">
         <f>B107/B128*100</f>
         <v>5.1148637626007289</v>
       </c>
-      <c r="C136" s="31">
+      <c r="C136" s="30">
         <f t="shared" ref="C136:I136" si="33">C107/C128*100</f>
         <v>14.768419240911957</v>
       </c>
-      <c r="D136" s="31">
+      <c r="D136" s="30">
         <f t="shared" si="33"/>
         <v>17.972885494359204</v>
       </c>
-      <c r="E136" s="31">
+      <c r="E136" s="30">
         <f t="shared" si="33"/>
         <v>0.34307817817274744</v>
       </c>
-      <c r="F136" s="31">
+      <c r="F136" s="30">
         <f t="shared" si="33"/>
         <v>7.9817047040581155</v>
       </c>
-      <c r="G136" s="31">
+      <c r="G136" s="30">
         <f t="shared" si="33"/>
         <v>0.67758959683156816</v>
       </c>
-      <c r="H136" s="31">
+      <c r="H136" s="30">
         <f t="shared" si="33"/>
         <v>2.4526947267598209</v>
       </c>
-      <c r="I136" s="33">
+      <c r="I136" s="32">
         <f t="shared" si="33"/>
         <v>9.2270609851760241</v>
       </c>
-      <c r="J136" s="52">
+      <c r="J136" s="50">
         <v>15.447254437412589</v>
       </c>
-      <c r="K136" s="53" t="s">
+      <c r="K136" s="51" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A137" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B137" s="34">
+      <c r="B137" s="33">
         <f>B108/B46*100</f>
         <v>0.44931732729037721</v>
       </c>
-      <c r="C137" s="34">
+      <c r="C137" s="33">
         <f t="shared" ref="C137:I137" si="34">C108/C46*100</f>
         <v>0.28784320856488443</v>
       </c>
-      <c r="D137" s="34">
+      <c r="D137" s="33">
         <f t="shared" si="34"/>
         <v>25.659935718986738</v>
       </c>
-      <c r="E137" s="34">
+      <c r="E137" s="33">
         <f t="shared" si="34"/>
         <v>0.16676401179154587</v>
       </c>
-      <c r="F137" s="34">
+      <c r="F137" s="33">
         <f t="shared" si="34"/>
         <v>0.65070161267710924</v>
       </c>
-      <c r="G137" s="34">
+      <c r="G137" s="33">
         <f t="shared" si="34"/>
         <v>5.033407111226806</v>
       </c>
-      <c r="H137" s="34">
+      <c r="H137" s="33">
         <f t="shared" si="34"/>
         <v>1.8719995618541665</v>
       </c>
-      <c r="I137" s="36">
+      <c r="I137" s="35">
         <f t="shared" si="34"/>
         <v>9.0595848876362481</v>
       </c>
-      <c r="J137" s="52">
+      <c r="J137" s="50">
         <v>7.5643762251545317</v>
       </c>
-      <c r="K137" s="53" t="s">
+      <c r="K137" s="51" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="H138" s="52">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="H138" s="50">
         <v>1.8719995618541665</v>
       </c>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A140" s="30" t="s">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A140" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B140" s="29" t="s">
+      <c r="B140" s="28" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A141" s="30" t="s">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A141" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B141" s="29" t="s">
+      <c r="B141" s="28" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A142" s="30"/>
-      <c r="B142" s="29"/>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A143" s="30" t="s">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A142" s="29"/>
+      <c r="B142" s="28"/>
+    </row>
+    <row r="143" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A143" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B143" s="29" t="s">
+      <c r="B143" s="28" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A144" s="30" t="s">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A144" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B144" s="29" t="s">
+      <c r="B144" s="28" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A147" s="40" t="s">
+    <row r="147" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A147" s="39" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="25" t="s">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A149" s="24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B151" s="44" t="s">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B151" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C151" s="45" t="s">
+      <c r="C151" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D151" s="45" t="s">
+      <c r="D151" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E151" s="45" t="s">
+      <c r="E151" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F151" s="46" t="s">
+      <c r="F151" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G151" s="46" t="s">
+      <c r="G151" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B152" s="47" t="s">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B152" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C152" s="48" t="s">
+      <c r="C152" t="s">
         <v>101</v>
       </c>
-      <c r="D152" s="48" t="s">
+      <c r="D152" t="s">
         <v>101</v>
       </c>
-      <c r="E152" s="48" t="s">
+      <c r="E152" t="s">
         <v>103</v>
       </c>
-      <c r="F152" s="49"/>
-      <c r="G152" s="49"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="44" t="s">
+      <c r="F152" s="47"/>
+      <c r="G152" s="47"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A153" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B153" s="2">
@@ -8606,8 +8522,8 @@
         <v>6428.5703532211328</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="47" t="s">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A154" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B154" s="5">
@@ -8635,8 +8551,8 @@
         <v>634.83870384962336</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="47" t="s">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A155" s="46" t="s">
         <v>7</v>
       </c>
       <c r="B155" s="5">
@@ -8664,8 +8580,8 @@
         <v>15149.928070463549</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="47" t="s">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A156" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B156" s="5">
@@ -8693,8 +8609,8 @@
         <v>4981.8058560754589</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="47" t="s">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A157" s="46" t="s">
         <v>167</v>
       </c>
       <c r="B157" s="5">
@@ -8722,8 +8638,8 @@
         <v>5378.5714066022902</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="47" t="s">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A158" s="46" t="s">
         <v>9</v>
       </c>
       <c r="B158" s="5">
@@ -8751,8 +8667,8 @@
         <v>2277.9121662753387</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="47" t="s">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B159" s="5">
@@ -8780,8 +8696,8 @@
         <v>5779.0603770187263</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="41" t="s">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B160" s="11">
@@ -8808,648 +8724,648 @@
         <f>SUM(B160:F160)</f>
         <v>40630.68693350612</v>
       </c>
-      <c r="H160" s="57">
+      <c r="H160" s="49">
         <v>40630.68693350612</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="25" t="s">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="24" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B165" s="44" t="s">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B165" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C165" s="45" t="s">
+      <c r="C165" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D165" s="45" t="s">
+      <c r="D165" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E165" s="45" t="s">
+      <c r="E165" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F165" s="46" t="s">
+      <c r="F165" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G165" s="46" t="s">
+      <c r="G165" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B166" s="47" t="s">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B166" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C166" s="48" t="s">
+      <c r="C166" t="s">
         <v>101</v>
       </c>
-      <c r="D166" s="48" t="s">
+      <c r="D166" t="s">
         <v>101</v>
       </c>
-      <c r="E166" s="48" t="s">
+      <c r="E166" t="s">
         <v>103</v>
       </c>
-      <c r="F166" s="49"/>
-      <c r="G166" s="49"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="44" t="s">
+      <c r="F166" s="47"/>
+      <c r="G166" s="47"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B167" s="54">
+      <c r="B167" s="52">
         <f>B153/B$160*100</f>
         <v>14.472379409661846</v>
       </c>
-      <c r="C167" s="31">
+      <c r="C167" s="30">
         <f t="shared" ref="C167:G167" si="42">C153/C$160*100</f>
         <v>31.182949727174496</v>
       </c>
-      <c r="D167" s="31">
+      <c r="D167" s="30">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="E167" s="31">
+      <c r="E167" s="30">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F167" s="32">
+      <c r="F167" s="31">
         <f t="shared" si="42"/>
         <v>0.83766987385998548</v>
       </c>
-      <c r="G167" s="32">
+      <c r="G167" s="31">
         <f t="shared" si="42"/>
         <v>15.821958323623145</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="47" t="s">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A168" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B168" s="55">
+      <c r="B168" s="53">
         <f t="shared" ref="B168:G168" si="43">B154/B$160*100</f>
         <v>3.2038285514613443</v>
       </c>
-      <c r="C168" s="37">
+      <c r="C168" s="36">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="D168" s="37">
+      <c r="D168" s="36">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="E168" s="37">
+      <c r="E168" s="36">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F168" s="38">
+      <c r="F168" s="37">
         <f t="shared" si="43"/>
         <v>4.6836350380629381E-2</v>
       </c>
-      <c r="G168" s="38">
+      <c r="G168" s="37">
         <f t="shared" si="43"/>
         <v>1.5624611636238501</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="47" t="s">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B169" s="55">
+      <c r="B169" s="53">
         <f t="shared" ref="B169:G169" si="44">B155/B$160*100</f>
         <v>35.422977589344974</v>
       </c>
-      <c r="C169" s="37">
+      <c r="C169" s="36">
         <f t="shared" si="44"/>
         <v>31.792992139245861</v>
       </c>
-      <c r="D169" s="37">
+      <c r="D169" s="36">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="E169" s="37">
+      <c r="E169" s="36">
         <f t="shared" si="44"/>
         <v>29.962769698777702</v>
       </c>
-      <c r="F169" s="38">
+      <c r="F169" s="37">
         <f t="shared" si="44"/>
         <v>91.151489857083035</v>
       </c>
-      <c r="G169" s="38">
+      <c r="G169" s="37">
         <f t="shared" si="44"/>
         <v>37.286910987394975</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="47" t="s">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B170" s="55">
+      <c r="B170" s="53">
         <f t="shared" ref="B170:G170" si="45">B156/B$160*100</f>
         <v>4.0904652810294202</v>
       </c>
-      <c r="C170" s="37">
+      <c r="C170" s="36">
         <f t="shared" si="45"/>
         <v>4.4955000921606008</v>
       </c>
-      <c r="D170" s="37">
+      <c r="D170" s="36">
         <f t="shared" si="45"/>
         <v>0</v>
       </c>
-      <c r="E170" s="37">
+      <c r="E170" s="36">
         <f t="shared" si="45"/>
         <v>70.037230301222294</v>
       </c>
-      <c r="F170" s="38">
+      <c r="F170" s="37">
         <f t="shared" si="45"/>
         <v>0.25370605358418596</v>
       </c>
-      <c r="G170" s="38">
+      <c r="G170" s="37">
         <f t="shared" si="45"/>
         <v>12.261190326977243</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="47" t="s">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B171" s="55">
+      <c r="B171" s="53">
         <f t="shared" ref="B171:G171" si="46">B157/B$160*100</f>
         <v>24.704925427007467</v>
       </c>
-      <c r="C171" s="37">
+      <c r="C171" s="36">
         <f t="shared" si="46"/>
         <v>4.0768074199934761</v>
       </c>
-      <c r="D171" s="37">
+      <c r="D171" s="36">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="E171" s="37">
+      <c r="E171" s="36">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="F171" s="38">
+      <c r="F171" s="37">
         <f t="shared" si="46"/>
         <v>0.98686383365391794</v>
       </c>
-      <c r="G171" s="38">
+      <c r="G171" s="37">
         <f t="shared" si="46"/>
         <v>13.237707291054553</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="47" t="s">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B172" s="55">
+      <c r="B172" s="53">
         <f t="shared" ref="B172:G172" si="47">B158/B$160*100</f>
         <v>1.9398315827305279</v>
       </c>
-      <c r="C172" s="37">
+      <c r="C172" s="36">
         <f t="shared" si="47"/>
         <v>6.6261153852143178</v>
       </c>
-      <c r="D172" s="37">
+      <c r="D172" s="36">
         <f t="shared" si="47"/>
         <v>100</v>
       </c>
-      <c r="E172" s="37">
+      <c r="E172" s="36">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
-      <c r="F172" s="38">
+      <c r="F172" s="37">
         <f t="shared" si="47"/>
         <v>3.4896390755981757</v>
       </c>
-      <c r="G172" s="38">
+      <c r="G172" s="37">
         <f t="shared" si="47"/>
         <v>5.6063835937680322</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="47" t="s">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B173" s="55">
+      <c r="B173" s="53">
         <f t="shared" ref="B173:G173" si="48">B159/B$160*100</f>
         <v>16.165592158764415</v>
       </c>
-      <c r="C173" s="37">
+      <c r="C173" s="36">
         <f t="shared" si="48"/>
         <v>21.825635236211248</v>
       </c>
-      <c r="D173" s="37">
+      <c r="D173" s="36">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="E173" s="37">
+      <c r="E173" s="36">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="F173" s="38">
+      <c r="F173" s="37">
         <f t="shared" si="48"/>
         <v>3.2337949558400831</v>
       </c>
-      <c r="G173" s="38">
+      <c r="G173" s="37">
         <f t="shared" si="48"/>
         <v>14.223388313558196</v>
       </c>
-      <c r="H173" s="56">
+      <c r="H173" s="50">
         <v>14.223388313558196</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="41" t="s">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A174" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B174" s="58">
+      <c r="B174" s="54">
         <f t="shared" ref="B174:G174" si="49">B160/B$160*100</f>
         <v>100</v>
       </c>
-      <c r="C174" s="26">
+      <c r="C174" s="25">
         <f t="shared" si="49"/>
         <v>100</v>
       </c>
-      <c r="D174" s="26">
+      <c r="D174" s="25">
         <f t="shared" si="49"/>
         <v>100</v>
       </c>
-      <c r="E174" s="26">
+      <c r="E174" s="25">
         <f t="shared" si="49"/>
         <v>100</v>
       </c>
-      <c r="F174" s="27">
+      <c r="F174" s="26">
         <f t="shared" si="49"/>
         <v>100</v>
       </c>
-      <c r="G174" s="27">
+      <c r="G174" s="26">
         <f t="shared" si="49"/>
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F175" s="56">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F175" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" s="30" t="s">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A177" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="B177" s="29" t="s">
+      <c r="B177" s="28" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" s="30" t="s">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B178" s="29" t="s">
+      <c r="B178" s="28" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" s="30"/>
-      <c r="B179" s="29"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" s="30" t="s">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A179" s="29"/>
+      <c r="B179" s="28"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A180" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="B180" s="29" t="s">
+      <c r="B180" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="30" t="s">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A181" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B181" s="29" t="s">
+      <c r="B181" s="28" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" s="25" t="s">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A184" s="24" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" s="46"/>
-      <c r="B186" s="44" t="s">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A186" s="45"/>
+      <c r="B186" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C186" s="45" t="s">
+      <c r="C186" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D186" s="45" t="s">
+      <c r="D186" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E186" s="45" t="s">
+      <c r="E186" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="F186" s="46" t="s">
+      <c r="F186" s="45" t="s">
         <v>63</v>
       </c>
-      <c r="G186" s="46" t="s">
+      <c r="G186" s="45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" s="60"/>
-      <c r="B187" s="47" t="s">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A187" s="56"/>
+      <c r="B187" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="C187" s="48" t="s">
+      <c r="C187" t="s">
         <v>101</v>
       </c>
-      <c r="D187" s="48" t="s">
+      <c r="D187" t="s">
         <v>101</v>
       </c>
-      <c r="E187" s="48" t="s">
+      <c r="E187" t="s">
         <v>103</v>
       </c>
-      <c r="F187" s="49"/>
-      <c r="G187" s="49"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" s="44" t="s">
+      <c r="F187" s="47"/>
+      <c r="G187" s="47"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A188" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B188" s="54">
+      <c r="B188" s="52">
         <f>B153/$G153*100</f>
         <v>44.501310096151386</v>
       </c>
-      <c r="C188" s="31">
+      <c r="C188" s="30">
         <f t="shared" ref="C188:G188" si="50">C153/$G153*100</f>
         <v>55.07345954060515</v>
       </c>
-      <c r="D188" s="31">
+      <c r="D188" s="30">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="E188" s="31">
+      <c r="E188" s="30">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="F188" s="32">
+      <c r="F188" s="31">
         <f t="shared" si="50"/>
         <v>0.42523036324345964</v>
       </c>
-      <c r="G188" s="32">
+      <c r="G188" s="31">
         <f t="shared" si="50"/>
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" s="47" t="s">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A189" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B189" s="55">
+      <c r="B189" s="53">
         <f t="shared" ref="B189:G189" si="51">B154/$G154*100</f>
         <v>99.759239397276318</v>
       </c>
-      <c r="C189" s="37">
+      <c r="C189" s="36">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="D189" s="37">
+      <c r="D189" s="36">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="E189" s="37">
+      <c r="E189" s="36">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="F189" s="38">
+      <c r="F189" s="37">
         <f t="shared" si="51"/>
         <v>0.2407606027236866</v>
       </c>
-      <c r="G189" s="38">
+      <c r="G189" s="37">
         <f t="shared" si="51"/>
         <v>100</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" s="47" t="s">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A190" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B190" s="55">
+      <c r="B190" s="53">
         <f t="shared" ref="B190:G190" si="52">B155/$G155*100</f>
         <v>46.219128439329502</v>
       </c>
-      <c r="C190" s="37">
+      <c r="C190" s="36">
         <f t="shared" si="52"/>
         <v>23.826507980786126</v>
       </c>
-      <c r="D190" s="37">
+      <c r="D190" s="36">
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="E190" s="37">
+      <c r="E190" s="36">
         <f t="shared" si="52"/>
         <v>10.319903082547954</v>
       </c>
-      <c r="F190" s="38">
+      <c r="F190" s="37">
         <f t="shared" si="52"/>
         <v>19.634460497336434</v>
       </c>
-      <c r="G190" s="38">
+      <c r="G190" s="37">
         <f t="shared" si="52"/>
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" s="47" t="s">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A191" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B191" s="55">
+      <c r="B191" s="53">
         <f t="shared" ref="B191:G191" si="53">B156/$G156*100</f>
         <v>16.230547506785399</v>
       </c>
-      <c r="C191" s="37">
+      <c r="C191" s="36">
         <f t="shared" si="53"/>
         <v>10.245443837701989</v>
       </c>
-      <c r="D191" s="37">
+      <c r="D191" s="36">
         <f t="shared" si="53"/>
         <v>0</v>
       </c>
-      <c r="E191" s="37">
+      <c r="E191" s="36">
         <f t="shared" si="53"/>
         <v>73.357816774654566</v>
       </c>
-      <c r="F191" s="38">
+      <c r="F191" s="37">
         <f t="shared" si="53"/>
         <v>0.16619188085804357</v>
       </c>
-      <c r="G191" s="38">
+      <c r="G191" s="37">
         <f t="shared" si="53"/>
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" s="47" t="s">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A192" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B192" s="55">
+      <c r="B192" s="53">
         <f t="shared" ref="B192:G192" si="54">B157/$G157*100</f>
         <v>90.795404276397747</v>
       </c>
-      <c r="C192" s="37">
+      <c r="C192" s="36">
         <f t="shared" si="54"/>
         <v>8.6058311921535839</v>
       </c>
-      <c r="D192" s="37">
+      <c r="D192" s="36">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="E192" s="37">
+      <c r="E192" s="36">
         <f t="shared" si="54"/>
         <v>0</v>
       </c>
-      <c r="F192" s="38">
+      <c r="F192" s="37">
         <f t="shared" si="54"/>
         <v>0.59876453144867803</v>
       </c>
-      <c r="G192" s="38">
+      <c r="G192" s="37">
         <f t="shared" si="54"/>
         <v>100</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="47" t="s">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A193" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B193" s="55">
+      <c r="B193" s="53">
         <f t="shared" ref="B193:G193" si="55">B158/$G158*100</f>
         <v>16.833495603303302</v>
       </c>
-      <c r="C193" s="37">
+      <c r="C193" s="36">
         <f t="shared" si="55"/>
         <v>33.026426500032308</v>
       </c>
-      <c r="D193" s="37">
+      <c r="D193" s="36">
         <f t="shared" si="55"/>
         <v>45.140776628389432</v>
       </c>
-      <c r="E193" s="37">
+      <c r="E193" s="36">
         <f t="shared" si="55"/>
         <v>0</v>
       </c>
-      <c r="F193" s="38">
+      <c r="F193" s="37">
         <f t="shared" si="55"/>
         <v>4.9993012682749578</v>
       </c>
-      <c r="G193" s="38">
+      <c r="G193" s="37">
         <f t="shared" si="55"/>
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="47" t="s">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A194" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B194" s="55">
+      <c r="B194" s="53">
         <f t="shared" ref="B194:G194" si="56">B159/$G159*100</f>
         <v>55.294462931939073</v>
       </c>
-      <c r="C194" s="37">
+      <c r="C194" s="36">
         <f t="shared" si="56"/>
         <v>42.879451940745327</v>
       </c>
-      <c r="D194" s="37">
+      <c r="D194" s="36">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="E194" s="37">
+      <c r="E194" s="36">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="F194" s="38">
+      <c r="F194" s="37">
         <f t="shared" si="56"/>
         <v>1.8260851273156014</v>
       </c>
-      <c r="G194" s="38">
+      <c r="G194" s="37">
         <f t="shared" si="56"/>
         <v>100</v>
       </c>
-      <c r="H194" s="56">
+      <c r="H194" s="50">
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="41" t="s">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A195" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B195" s="58">
+      <c r="B195" s="54">
         <f t="shared" ref="B195:G195" si="57">B160/$G160*100</f>
         <v>48.651148077134934</v>
       </c>
-      <c r="C195" s="26">
+      <c r="C195" s="25">
         <f t="shared" si="57"/>
         <v>27.943795863219488</v>
       </c>
-      <c r="D195" s="26">
+      <c r="D195" s="25">
         <f t="shared" si="57"/>
         <v>2.5307650949934994</v>
       </c>
-      <c r="E195" s="26">
+      <c r="E195" s="25">
         <f t="shared" si="57"/>
         <v>12.842514610830721</v>
       </c>
-      <c r="F195" s="27">
+      <c r="F195" s="26">
         <f t="shared" si="57"/>
         <v>8.0317763538213551</v>
       </c>
-      <c r="G195" s="27">
+      <c r="G195" s="26">
         <f t="shared" si="57"/>
         <v>100</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F196" s="56">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F196" s="50">
         <v>8.0317763538213551</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A198" s="40" t="s">
+    <row r="198" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A198" s="39" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" s="25" t="s">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A200" s="24" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B202" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C202" s="46" t="s">
+      <c r="C202" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D202" s="46" t="s">
+      <c r="D202" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="44" t="s">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A203" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B203" s="2">
@@ -9464,12 +9380,12 @@
         <f>SUM(B203:C203)</f>
         <v>3540.4360925205783</v>
       </c>
-      <c r="E203" s="53" t="s">
+      <c r="E203" s="51" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" s="47" t="s">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A204" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B204" s="5">
@@ -9484,12 +9400,12 @@
         <f t="shared" ref="D204:D211" si="60">SUM(B204:C204)</f>
         <v>0</v>
       </c>
-      <c r="E204" s="53" t="s">
+      <c r="E204" s="51" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" s="47" t="s">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A205" s="46" t="s">
         <v>7</v>
       </c>
       <c r="B205" s="5">
@@ -9504,12 +9420,12 @@
         <f t="shared" si="60"/>
         <v>3609.698820792355</v>
       </c>
-      <c r="E205" s="53" t="s">
+      <c r="E205" s="51" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" s="47" t="s">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A206" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B206" s="5">
@@ -9524,12 +9440,12 @@
         <f t="shared" si="60"/>
         <v>510.40812108755995</v>
       </c>
-      <c r="E206" s="53" t="s">
+      <c r="E206" s="51" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" s="47" t="s">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A207" s="46" t="s">
         <v>167</v>
       </c>
       <c r="B207" s="5">
@@ -9544,12 +9460,12 @@
         <f t="shared" si="60"/>
         <v>462.87077580163367</v>
       </c>
-      <c r="E207" s="53" t="s">
+      <c r="E207" s="51" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" s="47" t="s">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A208" s="46" t="s">
         <v>9</v>
       </c>
       <c r="B208" s="5">
@@ -9564,12 +9480,12 @@
         <f t="shared" si="60"/>
         <v>752.31298733021845</v>
       </c>
-      <c r="E208" s="53" t="s">
+      <c r="E208" s="51" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A209" s="47" t="s">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A209" s="46" t="s">
         <v>185</v>
       </c>
       <c r="B209" s="5">
@@ -9584,12 +9500,12 @@
         <f t="shared" si="60"/>
         <v>2478.0294169904005</v>
       </c>
-      <c r="E209" s="53" t="s">
+      <c r="E209" s="51" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A210" s="47" t="s">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A210" s="46" t="s">
         <v>14</v>
       </c>
       <c r="B210" s="5">
@@ -9604,12 +9520,12 @@
         <f t="shared" si="60"/>
         <v>151.14942615749058</v>
       </c>
-      <c r="E210" s="53" t="s">
+      <c r="E210" s="51" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A211" s="47" t="s">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A211" s="46" t="s">
         <v>15</v>
       </c>
       <c r="B211" s="8">
@@ -9624,12 +9540,12 @@
         <f t="shared" si="60"/>
         <v>2884.1236985985934</v>
       </c>
-      <c r="E211" s="53" t="s">
+      <c r="E211" s="51" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A212" s="41" t="s">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A212" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B212" s="11">
@@ -9644,389 +9560,389 @@
         <f>SUM(D203:D211)</f>
         <v>14389.02933927883</v>
       </c>
-      <c r="E212" s="53" t="s">
+      <c r="E212" s="51" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C213" s="51">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C213" s="49">
         <v>5774.3743051158172</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A215" s="30" t="s">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="B215" s="29" t="s">
+      <c r="B215" s="28" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A216" s="30" t="s">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="B216" s="29" t="s">
+      <c r="B216" s="28" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A217" s="30"/>
-      <c r="B217" s="29"/>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A218" s="30" t="s">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" s="29"/>
+      <c r="B217" s="28"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="B218" s="29" t="s">
+      <c r="B218" s="28" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="30" t="s">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="B219" s="29" t="s">
+      <c r="B219" s="28" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" s="30"/>
-      <c r="B220" s="29"/>
-      <c r="C220" s="29"/>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" s="30" t="s">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" s="29"/>
+      <c r="B220" s="28"/>
+      <c r="C220" s="28"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="B221" s="29" t="s">
+      <c r="B221" s="28" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" s="30" t="s">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="B222" s="29" t="s">
+      <c r="B222" s="28" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" s="30"/>
-      <c r="B223" s="29"/>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" s="30" t="s">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" s="29"/>
+      <c r="B223" s="28"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="B224" s="29" t="s">
+      <c r="B224" s="28" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" s="30" t="s">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B225" s="29" t="s">
+      <c r="B225" s="28" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B226" s="29"/>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B227" s="29"/>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" s="25" t="s">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B226" s="28"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B227" s="28"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" s="24" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B230" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C230" s="46" t="s">
+      <c r="C230" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="D230" s="46" t="s">
+      <c r="D230" s="45" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" s="44" t="s">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A231" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B231" s="54">
+      <c r="B231" s="52">
         <f>B203/B$212*100</f>
         <v>27.741298448086322</v>
       </c>
-      <c r="C231" s="32">
+      <c r="C231" s="31">
         <f t="shared" ref="C231:D231" si="63">C203/C$212*100</f>
         <v>19.926296225738795</v>
       </c>
-      <c r="D231" s="32">
+      <c r="D231" s="31">
         <f t="shared" si="63"/>
         <v>24.605107189933793</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" s="47" t="s">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B232" s="55">
+      <c r="B232" s="53">
         <f t="shared" ref="B232:D232" si="64">B204/B$212*100</f>
         <v>0</v>
       </c>
-      <c r="C232" s="38">
+      <c r="C232" s="37">
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
-      <c r="D232" s="38">
+      <c r="D232" s="37">
         <f t="shared" si="64"/>
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" s="47" t="s">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="B233" s="55">
+      <c r="B233" s="53">
         <f t="shared" ref="B233:D233" si="65">B205/B$212*100</f>
         <v>28.228726535922998</v>
       </c>
-      <c r="C233" s="38">
+      <c r="C233" s="37">
         <f t="shared" si="65"/>
         <v>20.39859813281933</v>
       </c>
-      <c r="D233" s="38">
+      <c r="D233" s="37">
         <f t="shared" si="65"/>
         <v>25.086465081690289</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A234" s="47" t="s">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A234" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B234" s="55">
+      <c r="B234" s="53">
         <f t="shared" ref="B234:D234" si="66">B206/B$212*100</f>
         <v>3.5841281117497505</v>
       </c>
-      <c r="C234" s="38">
+      <c r="C234" s="37">
         <f t="shared" si="66"/>
         <v>3.4921159873409664</v>
       </c>
-      <c r="D234" s="38">
+      <c r="D234" s="37">
         <f t="shared" si="66"/>
         <v>3.5472032828111622</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A235" s="47" t="s">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A235" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="B235" s="55">
+      <c r="B235" s="53">
         <f t="shared" ref="B235:D235" si="67">B207/B$212*100</f>
         <v>3.4056112419150852</v>
       </c>
-      <c r="C235" s="38">
+      <c r="C235" s="37">
         <f t="shared" si="67"/>
         <v>2.9351944738984983</v>
       </c>
-      <c r="D235" s="38">
+      <c r="D235" s="37">
         <f t="shared" si="67"/>
         <v>3.2168311349404233</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A236" s="47" t="s">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B236" s="55">
+      <c r="B236" s="53">
         <f t="shared" ref="B236:D236" si="68">B208/B$212*100</f>
         <v>5.2650776520829536</v>
       </c>
-      <c r="C236" s="38">
+      <c r="C236" s="37">
         <f t="shared" si="68"/>
         <v>5.1736291161068149</v>
       </c>
-      <c r="D236" s="38">
+      <c r="D236" s="37">
         <f t="shared" si="68"/>
         <v>5.2283789934083487</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A237" s="47" t="s">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="B237" s="55">
+      <c r="B237" s="53">
         <f t="shared" ref="B237:D237" si="69">B209/B$212*100</f>
         <v>15.598665446062068</v>
       </c>
-      <c r="C237" s="38">
+      <c r="C237" s="37">
         <f t="shared" si="69"/>
         <v>19.642962837966181</v>
       </c>
-      <c r="D237" s="38">
+      <c r="D237" s="37">
         <f t="shared" si="69"/>
         <v>17.221657962889374</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A238" s="47" t="s">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="B238" s="55">
+      <c r="B238" s="53">
         <f t="shared" ref="B238:D238" si="70">B210/B$212*100</f>
         <v>0.45269256069279734</v>
       </c>
-      <c r="C238" s="38">
+      <c r="C238" s="37">
         <f t="shared" si="70"/>
         <v>1.9422281577612006</v>
       </c>
-      <c r="D238" s="38">
+      <c r="D238" s="37">
         <f t="shared" si="70"/>
         <v>1.0504490789026781</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A239" s="47" t="s">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A239" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B239" s="55">
+      <c r="B239" s="53">
         <f t="shared" ref="B239:D239" si="71">B211/B$212*100</f>
         <v>15.723800003488014</v>
       </c>
-      <c r="C239" s="38">
+      <c r="C239" s="37">
         <f t="shared" si="71"/>
         <v>26.488975068368209</v>
       </c>
-      <c r="D239" s="38">
+      <c r="D239" s="37">
         <f t="shared" si="71"/>
         <v>20.04390727542393</v>
       </c>
-      <c r="E239" s="52">
+      <c r="E239" s="50">
         <v>20.04390727542393</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A240" s="41" t="s">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A240" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B240" s="58">
+      <c r="B240" s="54">
         <f>SUM(B231:B239)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="C240" s="27">
+      <c r="C240" s="26">
         <f t="shared" ref="C240:D240" si="72">SUM(C231:C239)</f>
         <v>100</v>
       </c>
-      <c r="D240" s="27">
+      <c r="D240" s="26">
         <f t="shared" si="72"/>
         <v>100</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B241" s="29"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B242" s="29"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" s="30" t="s">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B241" s="28"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B242" s="28"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A243" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B243" s="29" t="s">
+      <c r="B243" s="28" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" s="30" t="s">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A244" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="B244" s="62">
+      <c r="B244" s="57">
         <f>C238/100</f>
         <v>1.9422281577612006E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" s="30"/>
-      <c r="B245" s="29"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" s="30" t="s">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A245" s="29"/>
+      <c r="B245" s="28"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A246" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B246" s="29" t="s">
+      <c r="B246" s="28" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" s="30" t="s">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A247" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B247" s="62">
+      <c r="B247" s="57">
         <f>B237/100</f>
         <v>0.15598665446062068</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" s="30"/>
-      <c r="B248" s="29"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="30" t="s">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A248" s="29"/>
+      <c r="B248" s="28"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A249" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="B249" s="29" t="s">
+      <c r="B249" s="28" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="30" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A250" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B250" s="62">
+      <c r="B250" s="57">
         <f>B239/100</f>
         <v>0.15723800003488014</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" s="25" t="s">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A253" s="24" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B255" s="41" t="s">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B255" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C255" s="42" t="s">
+      <c r="C255" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D255" s="42" t="s">
+      <c r="D255" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="E255" s="42" t="s">
+      <c r="E255" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F255" s="43" t="s">
+      <c r="F255" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="G255" s="43" t="s">
+      <c r="G255" s="42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" s="44" t="s">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="43" t="s">
         <v>12</v>
       </c>
       <c r="B256" s="6">
@@ -10054,8 +9970,8 @@
         <v>8616.6805824517432</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A257" s="47" t="s">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A257" s="46" t="s">
         <v>13</v>
       </c>
       <c r="B257" s="8">
@@ -10083,8 +9999,8 @@
         <v>5775.3997392920746</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A258" s="41" t="s">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A258" s="40" t="s">
         <v>17</v>
       </c>
       <c r="B258" s="11">
@@ -10111,398 +10027,383 @@
         <f>SUM(B258:F258)</f>
         <v>14392.080321743819</v>
       </c>
-      <c r="H258" s="51">
+      <c r="H258" s="49">
         <v>14392.080321743819</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A261" s="25" t="s">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A261" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B263" s="41" t="s">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B263" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C263" s="42" t="s">
+      <c r="C263" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D263" s="42" t="s">
+      <c r="D263" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="E263" s="42" t="s">
+      <c r="E263" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F263" s="42" t="s">
+      <c r="F263" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="G263" s="24" t="s">
+      <c r="G263" s="23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A264" s="44" t="s">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A264" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="B264" s="54">
+      <c r="B264" s="52">
         <f>B256/$G256*100</f>
         <v>44.98234709805358</v>
       </c>
-      <c r="C264" s="65">
+      <c r="C264" s="30">
         <f t="shared" ref="C264:G264" si="79">C256/$G256*100</f>
         <v>2.9852132746545887</v>
       </c>
-      <c r="D264" s="65">
+      <c r="D264" s="30">
         <f t="shared" si="79"/>
         <v>44.017073704087565</v>
       </c>
-      <c r="E264" s="65">
+      <c r="E264" s="30">
         <f t="shared" si="79"/>
         <v>1.6865613333778926</v>
       </c>
-      <c r="F264" s="65">
+      <c r="F264" s="30">
         <f t="shared" si="79"/>
         <v>6.3288045898263743</v>
       </c>
-      <c r="G264" s="33">
+      <c r="G264" s="32">
         <f t="shared" si="79"/>
         <v>100</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A265" s="47" t="s">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A265" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B265" s="55">
+      <c r="B265" s="53">
         <f t="shared" ref="B265:G266" si="80">B257/$G257*100</f>
         <v>38.148935334254794</v>
       </c>
-      <c r="C265" s="37">
+      <c r="C265" s="36">
         <f t="shared" si="80"/>
         <v>0.43386829277250549</v>
       </c>
-      <c r="D265" s="37">
+      <c r="D265" s="36">
         <f t="shared" si="80"/>
         <v>57.725092233114452</v>
       </c>
-      <c r="E265" s="37">
+      <c r="E265" s="36">
         <f t="shared" si="80"/>
         <v>0.32634373148924734</v>
       </c>
-      <c r="F265" s="37">
+      <c r="F265" s="36">
         <f t="shared" si="80"/>
         <v>3.3657604083690118</v>
       </c>
-      <c r="G265" s="39">
+      <c r="G265" s="38">
         <f t="shared" si="80"/>
         <v>100</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A266" s="41" t="s">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A266" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B266" s="58">
+      <c r="B266" s="54">
         <f t="shared" si="80"/>
         <v>42.240166423902295</v>
       </c>
-      <c r="C266" s="26">
+      <c r="C266" s="25">
         <f t="shared" si="80"/>
         <v>1.9613837229987405</v>
       </c>
-      <c r="D266" s="26">
+      <c r="D266" s="25">
         <f t="shared" si="80"/>
         <v>49.517966199743128</v>
       </c>
-      <c r="E266" s="26">
+      <c r="E266" s="25">
         <f t="shared" si="80"/>
         <v>1.1407194392453615</v>
       </c>
-      <c r="F266" s="26">
+      <c r="F266" s="25">
         <f t="shared" si="80"/>
         <v>5.1397642141104685</v>
       </c>
-      <c r="G266" s="28">
+      <c r="G266" s="27">
         <f t="shared" si="80"/>
         <v>100</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F267" s="52">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F267" s="50">
         <v>5.1397642141104685</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="30" t="s">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A269" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="B269" s="29" t="s">
+      <c r="B269" s="28" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="30" t="s">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A270" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B270" s="29" t="s">
+      <c r="B270" s="28" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A271" s="30"/>
-      <c r="B271" s="29"/>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A272" s="30" t="s">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A271" s="29"/>
+      <c r="B271" s="28"/>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A272" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="B272" s="29" t="s">
+      <c r="B272" s="28" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A273" s="30" t="s">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A273" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="B273" s="29" t="s">
+      <c r="B273" s="28" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A274" s="30"/>
-      <c r="B274" s="29"/>
-    </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A275" s="30" t="s">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A274" s="29"/>
+      <c r="B274" s="28"/>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A275" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B275" s="29" t="s">
+      <c r="B275" s="28" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A276" s="30" t="s">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A276" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="B276" s="29" t="s">
+      <c r="B276" s="28" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A279" s="40" t="s">
+    <row r="279" spans="1:12" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A279" s="39" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A280" s="72"/>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A281" s="25" t="s">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A281" s="24" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A283" s="44" t="s">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A283" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="B283" s="45"/>
-      <c r="C283" s="46"/>
+      <c r="B283" s="44"/>
+      <c r="C283" s="45"/>
       <c r="D283" s="14">
         <f>SUM(B21:H22)</f>
         <v>16253.84598790595</v>
       </c>
-      <c r="L283" s="61"/>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A284" s="47" t="s">
+      <c r="L283" s="6"/>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A284" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="B284" s="48"/>
-      <c r="C284" s="49"/>
+      <c r="C284" s="47"/>
       <c r="D284" s="15">
         <f>U27</f>
         <v>-34.256569842259047</v>
       </c>
-      <c r="L284" s="61"/>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A285" s="47" t="s">
+      <c r="L284" s="6"/>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A285" s="46" t="s">
         <v>160</v>
       </c>
-      <c r="B285" s="48"/>
-      <c r="C285" s="49"/>
-      <c r="D285" s="70">
+      <c r="C285" s="47"/>
+      <c r="D285" s="15">
         <f>W27</f>
         <v>-88.289671394354244</v>
       </c>
-      <c r="E285" s="71" t="s">
+      <c r="E285" s="51" t="s">
         <v>194</v>
       </c>
-      <c r="F285" s="72"/>
-      <c r="L285" s="61"/>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A286" s="47" t="s">
+      <c r="L285" s="6"/>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A286" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B286" s="48"/>
-      <c r="C286" s="49"/>
+      <c r="C286" s="47"/>
       <c r="D286" s="15">
         <f>S27+T27</f>
         <v>2884.1236985985934</v>
       </c>
-      <c r="L286" s="61"/>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A287" s="47" t="s">
+      <c r="L286" s="6"/>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A287" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B287" s="48"/>
-      <c r="C287" s="49"/>
+      <c r="C287" s="47"/>
       <c r="D287" s="15">
         <f>SUM(I28:O28)</f>
         <v>3749.0182620505557</v>
       </c>
-      <c r="E287" s="61"/>
-      <c r="L287" s="61"/>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A288" s="47" t="s">
+      <c r="E287" s="6"/>
+      <c r="L287" s="6"/>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A288" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B288" s="48"/>
-      <c r="C288" s="49"/>
+      <c r="C288" s="47"/>
       <c r="D288" s="15">
         <f>SUM(W14:W20)</f>
         <v>3263.3659055205276</v>
       </c>
-      <c r="L288" s="61"/>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A289" s="50" t="s">
+      <c r="L288" s="6"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="B289" s="59"/>
-      <c r="C289" s="60"/>
+      <c r="B289" s="55"/>
+      <c r="C289" s="56"/>
       <c r="D289" s="16">
         <f>SUM(S14:W20)-SUM(I28:O28)</f>
         <v>17114.373006678386</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A292" s="25" t="s">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A294" s="44" t="s">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A294" s="43" t="s">
         <v>178</v>
       </c>
-      <c r="B294" s="45"/>
-      <c r="C294" s="45"/>
-      <c r="D294" s="45"/>
-      <c r="E294" s="33">
+      <c r="B294" s="44"/>
+      <c r="C294" s="44"/>
+      <c r="D294" s="44"/>
+      <c r="E294" s="32">
         <f>SUM(D287:D288)/$D$289*100</f>
         <v>40.973655095834964</v>
       </c>
-      <c r="F294" s="53" t="s">
+      <c r="F294" s="51" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A295" s="47" t="s">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A295" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="B295" s="48"/>
-      <c r="C295" s="48"/>
-      <c r="D295" s="48"/>
-      <c r="E295" s="39">
+      <c r="E295" s="38">
         <f>D284/D$289*100</f>
         <v>-0.20016257580041885</v>
       </c>
-      <c r="F295" s="53"/>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A296" s="47" t="s">
+      <c r="F295" s="51"/>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A296" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="B296" s="48"/>
-      <c r="C296" s="48"/>
-      <c r="D296" s="48"/>
-      <c r="E296" s="39">
+      <c r="E296" s="38">
         <f t="shared" ref="E296" si="81">D285/D$289*100</f>
         <v>-0.51588025667023718</v>
       </c>
-      <c r="F296" s="53"/>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A297" s="50" t="s">
+      <c r="F296" s="51"/>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A297" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="B297" s="59"/>
-      <c r="C297" s="59"/>
-      <c r="D297" s="59"/>
-      <c r="E297" s="36">
+      <c r="B297" s="55"/>
+      <c r="C297" s="55"/>
+      <c r="D297" s="55"/>
+      <c r="E297" s="35">
         <f>D286/V29*100</f>
         <v>55.272568898996376</v>
       </c>
-      <c r="F297" s="53" t="s">
+      <c r="F297" s="51" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A300" s="30" t="s">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A300" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="B300" s="29" t="s">
+      <c r="B300" s="28" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A301" s="30" t="s">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A301" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="B301" s="29" t="s">
+      <c r="B301" s="28" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A302" s="30"/>
-      <c r="B302" s="29"/>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A303" s="30" t="s">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A302" s="29"/>
+      <c r="B302" s="28"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A303" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="B303" s="29" t="s">
+      <c r="B303" s="28" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A304" s="30" t="s">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="B304" s="29" t="s">
+      <c r="B304" s="28" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B305" s="29" t="s">
+    <row r="305" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B305" s="28" t="s">
         <v>209</v>
       </c>
     </row>
